--- a/ZonasEscolares/excels/LIMA-LIMA-COMAS.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-COMAS.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7350,7 +7350,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7714,7 +7714,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-COMAS.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-COMAS.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>ANGELITOS DE SANTA MARIA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-11.91243</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.02597</v>
-      </c>
-      <c r="I2" t="n">
-        <v>213</v>
-      </c>
-      <c r="J2" t="n">
-        <v>11</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-11.91243</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.02597</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>MARIO VARGAS LLOSA</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-11.92458</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.05362</v>
-      </c>
-      <c r="I3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J3" t="n">
-        <v>18</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-11.92458</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.05362</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>LA PASCANA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-11.93643</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-77.04637</v>
-      </c>
-      <c r="I4" t="n">
-        <v>390</v>
-      </c>
-      <c r="J4" t="n">
-        <v>22</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-11.93643</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-77.04637</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>SANGARARA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-11.915543</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-77.055633</v>
-      </c>
-      <c r="I5" t="n">
-        <v>336</v>
-      </c>
-      <c r="J5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-11.915543</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-77.055633</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>LUIS ENRIQUE XIV</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-11.9141</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-77.0112</v>
-      </c>
-      <c r="I6" t="n">
-        <v>290</v>
-      </c>
-      <c r="J6" t="n">
-        <v>17</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-11.9141</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-77.0112</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>03</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-11.9662</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-77.05441</v>
-      </c>
-      <c r="I7" t="n">
-        <v>209</v>
-      </c>
-      <c r="J7" t="n">
-        <v>11</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-11.9662</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-77.05441</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>317</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-11.92047</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.04411</v>
-      </c>
-      <c r="I8" t="n">
-        <v>237</v>
-      </c>
-      <c r="J8" t="n">
-        <v>11</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-11.92047</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.04411</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>326 MARIA MONTESSORI</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-11.95697</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-77.05620999999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>296</v>
-      </c>
-      <c r="J9" t="n">
-        <v>13</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-11.95697</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-77.05621</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>334</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-11.94098</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-77.06309</v>
-      </c>
-      <c r="I10" t="n">
-        <v>348</v>
-      </c>
-      <c r="J10" t="n">
-        <v>15</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-11.94098</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-77.06309</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>337 SANGARARA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-11.92474</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-77.04515000000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>265</v>
-      </c>
-      <c r="J11" t="n">
-        <v>14</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-11.92474</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-77.04515</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>341 EL RETABLO</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-11.93803</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.05577</v>
-      </c>
-      <c r="I12" t="n">
-        <v>213</v>
-      </c>
-      <c r="J12" t="n">
-        <v>11</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-11.93803</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.05577</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>354 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-11.92742</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-77.056</v>
-      </c>
-      <c r="I13" t="n">
-        <v>167</v>
-      </c>
-      <c r="J13" t="n">
-        <v>10</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-11.92742</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-77.056</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>356 ANGELITOS DEL ALAMO</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-11.93107</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-77.06793999999999</v>
-      </c>
-      <c r="I14" t="n">
-        <v>240</v>
-      </c>
-      <c r="J14" t="n">
-        <v>11</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-11.93107</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-77.06794</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>369</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-11.93322</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-77.05404</v>
-      </c>
-      <c r="I15" t="n">
-        <v>240</v>
-      </c>
-      <c r="J15" t="n">
-        <v>10</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-11.93322</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-77.05404</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>370 VIRGEN DE LA PUERTA</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-11.95692</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-77.03582</v>
-      </c>
-      <c r="I16" t="n">
-        <v>241</v>
-      </c>
-      <c r="J16" t="n">
-        <v>10</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-11.95692</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-77.03582</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>373</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-11.95157</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-77.0574</v>
-      </c>
-      <c r="I17" t="n">
-        <v>216</v>
-      </c>
-      <c r="J17" t="n">
-        <v>10</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-11.95157</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-77.0574</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>868</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-11.9098</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-77.04598</v>
-      </c>
-      <c r="I18" t="n">
-        <v>204</v>
-      </c>
-      <c r="J18" t="n">
-        <v>11</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-11.9098</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-77.04598</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>CARMEN ALTO</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-11.94631</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-77.03113999999999</v>
-      </c>
-      <c r="I19" t="n">
-        <v>304</v>
-      </c>
-      <c r="J19" t="n">
-        <v>14</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-11.94631</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-77.03114</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>888 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-11.91563</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-77.03456</v>
-      </c>
-      <c r="I20" t="n">
-        <v>331</v>
-      </c>
-      <c r="J20" t="n">
-        <v>17</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-11.91563</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-77.03456</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>LUIS ENRIQUE II</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-11.91925</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-77.03833</v>
-      </c>
-      <c r="I21" t="n">
-        <v>238</v>
-      </c>
-      <c r="J21" t="n">
-        <v>16</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-11.91925</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-77.03833</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>LUIS ENRIQUE XIII</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-11.90842</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-77.04148000000001</v>
-      </c>
-      <c r="I22" t="n">
-        <v>275</v>
-      </c>
-      <c r="J22" t="n">
-        <v>17</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-11.90842</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-77.04148</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>371</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-11.94334</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-77.05569</v>
-      </c>
-      <c r="I23" t="n">
-        <v>312</v>
-      </c>
-      <c r="J23" t="n">
-        <v>17</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-11.94334</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-77.05569</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>368 ANGELITOS DE JESUS</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-11.91963</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-77.05964</v>
-      </c>
-      <c r="I24" t="n">
-        <v>388</v>
-      </c>
-      <c r="J24" t="n">
-        <v>15</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-11.91963</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-77.05964</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>02 JOSE GALVITO</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-11.911038</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-77.012883</v>
-      </c>
-      <c r="I25" t="n">
-        <v>208</v>
-      </c>
-      <c r="J25" t="n">
-        <v>9</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-11.911038</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-77.012883</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>12</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-11.9381</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-77.04255999999999</v>
-      </c>
-      <c r="I26" t="n">
-        <v>379</v>
-      </c>
-      <c r="J26" t="n">
-        <v>18</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-11.9381</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-77.04256</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>054</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-11.959535</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-77.04419</v>
-      </c>
-      <c r="I27" t="n">
-        <v>362</v>
-      </c>
-      <c r="J27" t="n">
-        <v>11</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-11.959535</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-77.04419</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>316 SAN FELIPE</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-11.90046</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-77.04003</v>
-      </c>
-      <c r="I28" t="n">
-        <v>264</v>
-      </c>
-      <c r="J28" t="n">
-        <v>11</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-11.90046</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-77.04003</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>328</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-11.90765</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-77.03788</v>
-      </c>
-      <c r="I29" t="n">
-        <v>284</v>
-      </c>
-      <c r="J29" t="n">
-        <v>13</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-11.90765</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-77.03788</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-11.93058</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-77.05647999999999</v>
-      </c>
-      <c r="I30" t="n">
-        <v>678</v>
-      </c>
-      <c r="J30" t="n">
-        <v>23</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-11.93058</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-77.05648</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>2016 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-11.94477</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-77.05477</v>
-      </c>
-      <c r="I31" t="n">
-        <v>482</v>
-      </c>
-      <c r="J31" t="n">
-        <v>23</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-11.94477</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-77.05477</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>2020 MAESTRO JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-11.93864</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-77.05562</v>
-      </c>
-      <c r="I32" t="n">
-        <v>639</v>
-      </c>
-      <c r="J32" t="n">
-        <v>26</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-11.93864</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-77.05562</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>2033 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-11.95544</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-77.05324</v>
-      </c>
-      <c r="I33" t="n">
-        <v>604</v>
-      </c>
-      <c r="J33" t="n">
-        <v>25</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-11.95544</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-77.05324</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>2035 FERNANDO BELAUNDE TERRY</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-11.94199</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-77.03513</v>
-      </c>
-      <c r="I34" t="n">
-        <v>368</v>
-      </c>
-      <c r="J34" t="n">
-        <v>14</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-11.94199</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-77.03513</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>2042 FRAY MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-11.96187</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-77.04706</v>
-      </c>
-      <c r="I35" t="n">
-        <v>511</v>
-      </c>
-      <c r="J35" t="n">
-        <v>22</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-11.96187</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-77.04706</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>2043 SANGARARA</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-11.91968</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-77.0442</v>
-      </c>
-      <c r="I36" t="n">
-        <v>570</v>
-      </c>
-      <c r="J36" t="n">
-        <v>25</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-11.91968</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-77.0442</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>2046 VIRGEN DE LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-11.97198</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-77.05695</v>
-      </c>
-      <c r="I37" t="n">
-        <v>432</v>
-      </c>
-      <c r="J37" t="n">
-        <v>19</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-11.97198</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-77.05695</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>2055 PRIMERO DE ABRIL</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-11.91554</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-77.04418</v>
-      </c>
-      <c r="I38" t="n">
-        <v>670</v>
-      </c>
-      <c r="J38" t="n">
-        <v>33</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-11.91554</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-77.04418</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>2059 SUECIA</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-11.92514</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-77.03878</v>
-      </c>
-      <c r="I39" t="n">
-        <v>659</v>
-      </c>
-      <c r="J39" t="n">
-        <v>31</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-11.92514</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-77.03878</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>2060</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-11.91124</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-77.01776</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1069</v>
-      </c>
-      <c r="J40" t="n">
-        <v>39</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-11.91124</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-77.01776</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1069</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>2072 LEV SEMIONOVICH VIGOTSKI</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-11.90473</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-77.05477</v>
-      </c>
-      <c r="I41" t="n">
-        <v>354</v>
-      </c>
-      <c r="J41" t="n">
-        <v>15</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-11.90473</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-77.05477</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>2077 SAN MARTIN DE PORRES DE AÑO NUEVO / SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-11.92842</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-77.04119</v>
-      </c>
-      <c r="I42" t="n">
-        <v>942</v>
-      </c>
-      <c r="J42" t="n">
-        <v>42</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-11.92842</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-77.04119</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>2097</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-11.90724</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-77.03831</v>
-      </c>
-      <c r="I43" t="n">
-        <v>681</v>
-      </c>
-      <c r="J43" t="n">
-        <v>28</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-11.90724</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-77.03831</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>2100 JUAN VELASCO ALVARADO</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-11.95464</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-77.05504000000001</v>
-      </c>
-      <c r="I44" t="n">
-        <v>661</v>
-      </c>
-      <c r="J44" t="n">
-        <v>29</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-11.95464</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-77.05504</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>3060 ALFONSO UGARTE VERNAL</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-11.93905</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-77.05315</v>
-      </c>
-      <c r="I45" t="n">
-        <v>557</v>
-      </c>
-      <c r="J45" t="n">
-        <v>23</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-11.93905</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-77.05315</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>3062 SANTA ROSA</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-11.94918</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-77.04859999999999</v>
-      </c>
-      <c r="I46" t="n">
-        <v>792</v>
-      </c>
-      <c r="J46" t="n">
-        <v>38</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-11.94918</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-77.0486</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>3064</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-11.94199</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-77.04259</v>
-      </c>
-      <c r="I47" t="n">
-        <v>709</v>
-      </c>
-      <c r="J47" t="n">
-        <v>29</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-11.94199</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-77.04259</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>8160 LOS CHASQUIS</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-11.93434</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-77.06113999999999</v>
-      </c>
-      <c r="I48" t="n">
-        <v>907</v>
-      </c>
-      <c r="J48" t="n">
-        <v>39</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-11.93434</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-77.06114</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>8162</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-11.96378</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-77.06124</v>
-      </c>
-      <c r="I49" t="n">
-        <v>340</v>
-      </c>
-      <c r="J49" t="n">
-        <v>14</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-11.96378</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-77.06124</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>2047</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-11.95767</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-77.04013999999999</v>
-      </c>
-      <c r="I50" t="n">
-        <v>571</v>
-      </c>
-      <c r="J50" t="n">
-        <v>30</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-11.95767</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-77.04014</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>3072 AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-11.94652</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-77.06183</v>
-      </c>
-      <c r="I51" t="n">
-        <v>732</v>
-      </c>
-      <c r="J51" t="n">
-        <v>22</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-11.94652</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-77.06183</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>3077 EL ALAMO</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-11.93319</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-77.06758000000001</v>
-      </c>
-      <c r="I52" t="n">
-        <v>508</v>
-      </c>
-      <c r="J52" t="n">
-        <v>21</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-11.93319</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-77.06758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>3082 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-11.965354</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-77.059168</v>
-      </c>
-      <c r="I53" t="n">
-        <v>813</v>
-      </c>
-      <c r="J53" t="n">
-        <v>35</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-11.965354</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-77.059168</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>3085 PEDRO VILCA APAZA</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-11.95164</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-77.05717</v>
-      </c>
-      <c r="I54" t="n">
-        <v>389</v>
-      </c>
-      <c r="J54" t="n">
-        <v>15</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-11.95164</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-77.05717</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>8156 PERUANO ALEMAN</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-11.90871</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-77.04277999999999</v>
-      </c>
-      <c r="I55" t="n">
-        <v>309</v>
-      </c>
-      <c r="J55" t="n">
-        <v>14</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-11.90871</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-77.04278</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>8157 REPUBLICA DE FRANCIA</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-11.91219</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-77.04131</v>
-      </c>
-      <c r="I56" t="n">
-        <v>522</v>
-      </c>
-      <c r="J56" t="n">
-        <v>21</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-11.91219</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-77.04131</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>8158 ISABEL FLORES DE OLIVA</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-11.91616</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-77.050005</v>
-      </c>
-      <c r="I57" t="n">
-        <v>503</v>
-      </c>
-      <c r="J57" t="n">
-        <v>24</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-11.91616</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-77.050005</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>8173 SANTA ISOLINA</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-11.95911</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-77.06225999999999</v>
-      </c>
-      <c r="I58" t="n">
-        <v>446</v>
-      </c>
-      <c r="J58" t="n">
-        <v>19</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-11.95911</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-77.06226</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>2022 SINCHI ROCA</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-11.93045</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-77.04964</v>
-      </c>
-      <c r="I59" t="n">
-        <v>1787</v>
-      </c>
-      <c r="J59" t="n">
-        <v>84</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-11.93045</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-77.04964</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1787</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>2048 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-11.939926</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-77.063361</v>
-      </c>
-      <c r="I60" t="n">
-        <v>1662</v>
-      </c>
-      <c r="J60" t="n">
-        <v>75</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-11.939926</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-77.063361</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1662</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>3055 TUPAC AMARU</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-11.93503</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-77.04317</v>
-      </c>
-      <c r="I61" t="n">
-        <v>1811</v>
-      </c>
-      <c r="J61" t="n">
-        <v>87</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-11.93503</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-77.04317</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1811</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>ESTADOS UNIDOS</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-11.965191</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-77.05676</v>
-      </c>
-      <c r="I62" t="n">
-        <v>1751</v>
-      </c>
-      <c r="J62" t="n">
-        <v>91</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-11.965191</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-77.05676</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1751</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3693,20 +4291,30 @@
           <t>2075 CRISTO HIJO DE DIOS</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>-11.92201</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-77.02409</v>
-      </c>
-      <c r="I63" t="n">
-        <v>694</v>
-      </c>
-      <c r="J63" t="n">
-        <v>41</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-11.92201</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-77.02409</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3745,20 +4353,30 @@
           <t>PERU-HOLANDA</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-11.91663</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-77.03561000000001</v>
-      </c>
-      <c r="I64" t="n">
-        <v>1745</v>
-      </c>
-      <c r="J64" t="n">
-        <v>73</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-11.91663</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-77.03561</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1745</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3797,20 +4415,30 @@
           <t>LIBERTAD</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>-11.9224</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-77.03899</v>
-      </c>
-      <c r="I65" t="n">
-        <v>1069</v>
-      </c>
-      <c r="J65" t="n">
-        <v>52</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-11.9224</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-77.03899</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1069</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3849,20 +4477,30 @@
           <t>2026 SIMON BOLIVAR</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>-11.95063</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-77.06313</v>
-      </c>
-      <c r="I66" t="n">
-        <v>942</v>
-      </c>
-      <c r="J66" t="n">
-        <v>50</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-11.95063</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-77.06313</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3901,20 +4539,30 @@
           <t>3061 JORGE CHAVEZ DARTNELL</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>-11.95925</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-77.0521</v>
-      </c>
-      <c r="I67" t="n">
-        <v>665</v>
-      </c>
-      <c r="J67" t="n">
-        <v>31</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-11.95925</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-77.0521</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3953,20 +4601,30 @@
           <t>3076 SANTA ROSA</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>-11.91084</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-77.00576</v>
-      </c>
-      <c r="I68" t="n">
-        <v>1071</v>
-      </c>
-      <c r="J68" t="n">
-        <v>48</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-11.91084</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-77.00576</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1071</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4005,20 +4663,30 @@
           <t>8170 CESAR VALLEJO</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>-11.93162</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-77.03668</v>
-      </c>
-      <c r="I69" t="n">
-        <v>419</v>
-      </c>
-      <c r="J69" t="n">
-        <v>24</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-11.93162</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-77.03668</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4057,20 +4725,30 @@
           <t>3047 REPUBLICA DE CANADA</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>-11.95916</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-77.04107</v>
-      </c>
-      <c r="I70" t="n">
-        <v>933</v>
-      </c>
-      <c r="J70" t="n">
-        <v>66</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-11.95916</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-77.04107</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>933</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4109,20 +4787,30 @@
           <t>3065 VIRGEN DEL CARMEN</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>-11.93866</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-77.04106</v>
-      </c>
-      <c r="I71" t="n">
-        <v>887</v>
-      </c>
-      <c r="J71" t="n">
-        <v>42</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-11.93866</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-77.04106</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4161,20 +4849,30 @@
           <t>3066 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>-11.94171</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-77.04826</v>
-      </c>
-      <c r="I72" t="n">
-        <v>880</v>
-      </c>
-      <c r="J72" t="n">
-        <v>39</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-11.94171</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-77.04826</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>880</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4213,20 +4911,30 @@
           <t>2085 SAN AGUSTIN</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>-11.9323</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-77.05056</v>
-      </c>
-      <c r="I73" t="n">
-        <v>1844</v>
-      </c>
-      <c r="J73" t="n">
-        <v>79</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-11.9323</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-77.05056</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1844</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4265,20 +4973,30 @@
           <t>3096 FRANZ TAMAYO SOLARES</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>-11.92383</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-77.05296</v>
-      </c>
-      <c r="I74" t="n">
-        <v>926</v>
-      </c>
-      <c r="J74" t="n">
-        <v>41</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-11.92383</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-77.05296</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4317,20 +5035,30 @@
           <t>CORONEL JOSE GALVEZ</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>-11.91142</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-77.01487</v>
-      </c>
-      <c r="I75" t="n">
-        <v>494</v>
-      </c>
-      <c r="J75" t="n">
-        <v>37</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-11.91142</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-77.01487</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4369,20 +5097,30 @@
           <t>2038 INCA GARCILASO DE LA VEGA</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>-11.917908</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-77.029028</v>
-      </c>
-      <c r="I76" t="n">
-        <v>1135</v>
-      </c>
-      <c r="J76" t="n">
-        <v>33</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-11.917908</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-77.029028</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1135</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4421,20 +5159,30 @@
           <t>2031 JOSE VALVERDE CARO</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>-11.94512</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-77.03126</v>
-      </c>
-      <c r="I77" t="n">
-        <v>1286</v>
-      </c>
-      <c r="J77" t="n">
-        <v>53</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-11.94512</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-77.03126</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4473,20 +5221,30 @@
           <t>JOSE MARTI</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>-11.95403</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-77.05587</v>
-      </c>
-      <c r="I78" t="n">
-        <v>711</v>
-      </c>
-      <c r="J78" t="n">
-        <v>32</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-11.95403</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-77.05587</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4525,20 +5283,30 @@
           <t>RAMON CASTILLA</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>-11.93282</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-77.05559</v>
-      </c>
-      <c r="I79" t="n">
-        <v>760</v>
-      </c>
-      <c r="J79" t="n">
-        <v>43</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-11.93282</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-77.05559</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4577,20 +5345,30 @@
           <t>EL AMAUTA</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>-11.92998</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-77.06647</v>
-      </c>
-      <c r="I80" t="n">
-        <v>835</v>
-      </c>
-      <c r="J80" t="n">
-        <v>37</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-11.92998</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-77.06647</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4629,20 +5407,30 @@
           <t>JUAN PABLO VIZCARDO Y GUZMAN</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v>-11.92554</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-77.04526</v>
-      </c>
-      <c r="I81" t="n">
-        <v>354</v>
-      </c>
-      <c r="J81" t="n">
-        <v>26</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-11.92554</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-77.04526</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4681,20 +5469,30 @@
           <t>MARISCAL ANDRES AVELINO CACERES DORREGARAY</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>-11.91639</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-77.03376</v>
-      </c>
-      <c r="I82" t="n">
-        <v>700</v>
-      </c>
-      <c r="J82" t="n">
-        <v>60</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-11.91639</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-77.03376</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4733,20 +5531,30 @@
           <t>LA ALBORADA FRANCESA</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>-11.9123</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-77.04734000000001</v>
-      </c>
-      <c r="I83" t="n">
-        <v>673</v>
-      </c>
-      <c r="J83" t="n">
-        <v>37</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-11.9123</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-77.04734</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4785,20 +5593,30 @@
           <t>PERUANO SUIZO</t>
         </is>
       </c>
-      <c r="G84" t="n">
-        <v>-11.96703</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-77.06010999999999</v>
-      </c>
-      <c r="I84" t="n">
-        <v>785</v>
-      </c>
-      <c r="J84" t="n">
-        <v>38</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-11.96703</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-77.06011</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>785</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4837,20 +5655,30 @@
           <t>SAN CARLOS</t>
         </is>
       </c>
-      <c r="G85" t="n">
-        <v>-11.90316</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-77.04262</v>
-      </c>
-      <c r="I85" t="n">
-        <v>375</v>
-      </c>
-      <c r="J85" t="n">
-        <v>19</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-11.90316</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-77.04262</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4889,20 +5717,30 @@
           <t>SAN FELIPE</t>
         </is>
       </c>
-      <c r="G86" t="n">
-        <v>-11.89896</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-77.04062999999999</v>
-      </c>
-      <c r="I86" t="n">
-        <v>1427</v>
-      </c>
-      <c r="J86" t="n">
-        <v>65</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-11.89896</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-77.04063</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1427</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4941,20 +5779,30 @@
           <t>COMERCIO 62 ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G87" t="n">
-        <v>-11.93902</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-77.05314</v>
-      </c>
-      <c r="I87" t="n">
-        <v>681</v>
-      </c>
-      <c r="J87" t="n">
-        <v>36</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-11.93902</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-77.05314</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4993,20 +5841,30 @@
           <t>CARLOS WIESSE</t>
         </is>
       </c>
-      <c r="G88" t="n">
-        <v>-11.9519</v>
-      </c>
-      <c r="H88" t="n">
-        <v>-77.0505</v>
-      </c>
-      <c r="I88" t="n">
-        <v>1782</v>
-      </c>
-      <c r="J88" t="n">
-        <v>90</v>
-      </c>
-      <c r="K88" t="n">
-        <v>1</v>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-11.9519</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-77.0505</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1782</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -5045,20 +5903,30 @@
           <t>SANTA LUZMILA</t>
         </is>
       </c>
-      <c r="G89" t="n">
-        <v>-11.945741</v>
-      </c>
-      <c r="H89" t="n">
-        <v>-77.05905300000001</v>
-      </c>
-      <c r="I89" t="n">
-        <v>365</v>
-      </c>
-      <c r="J89" t="n">
-        <v>17</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-11.945741</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-77.059053</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -5097,20 +5965,30 @@
           <t>3068 SAN JUDAS TADEO</t>
         </is>
       </c>
-      <c r="G90" t="n">
-        <v>-11.95762</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-77.05009</v>
-      </c>
-      <c r="I90" t="n">
-        <v>473</v>
-      </c>
-      <c r="J90" t="n">
-        <v>23</v>
-      </c>
-      <c r="K90" t="n">
-        <v>2</v>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-11.95762</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-77.05009</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -5149,20 +6027,30 @@
           <t>LUIS ENRIQUE XVII</t>
         </is>
       </c>
-      <c r="G91" t="n">
-        <v>-11.93585</v>
-      </c>
-      <c r="H91" t="n">
-        <v>-77.05155000000001</v>
-      </c>
-      <c r="I91" t="n">
-        <v>381</v>
-      </c>
-      <c r="J91" t="n">
-        <v>16</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-11.93585</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-77.05155</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -5201,20 +6089,30 @@
           <t>01</t>
         </is>
       </c>
-      <c r="G92" t="n">
-        <v>-11.92054</v>
-      </c>
-      <c r="H92" t="n">
-        <v>-77.03962</v>
-      </c>
-      <c r="I92" t="n">
-        <v>274</v>
-      </c>
-      <c r="J92" t="n">
-        <v>11</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-11.92054</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-77.03962</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -5253,20 +6151,30 @@
           <t>8186 MARIA JESUS ESPINOZA MATOS</t>
         </is>
       </c>
-      <c r="G93" t="n">
-        <v>-11.89907</v>
-      </c>
-      <c r="H93" t="n">
-        <v>-77.04858</v>
-      </c>
-      <c r="I93" t="n">
-        <v>550</v>
-      </c>
-      <c r="J93" t="n">
-        <v>25</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-11.89907</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-77.04858</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -5305,20 +6213,30 @@
           <t>ESPIRITU SANTO</t>
         </is>
       </c>
-      <c r="G94" t="n">
-        <v>-11.93762</v>
-      </c>
-      <c r="H94" t="n">
-        <v>-77.05025000000001</v>
-      </c>
-      <c r="I94" t="n">
-        <v>24</v>
-      </c>
-      <c r="J94" t="n">
-        <v>2</v>
-      </c>
-      <c r="K94" t="n">
-        <v>1</v>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-11.93762</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-77.05025</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -5357,20 +6275,30 @@
           <t>LA SEMILLITA</t>
         </is>
       </c>
-      <c r="G95" t="n">
-        <v>-11.95989</v>
-      </c>
-      <c r="H95" t="n">
-        <v>-77.04742</v>
-      </c>
-      <c r="I95" t="n">
-        <v>251</v>
-      </c>
-      <c r="J95" t="n">
-        <v>15</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-11.95989</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-77.04742</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -5409,20 +6337,30 @@
           <t>PAUL GROUSSAC DE HUAQUILLAY</t>
         </is>
       </c>
-      <c r="G96" t="n">
-        <v>-11.946962</v>
-      </c>
-      <c r="H96" t="n">
-        <v>-77.050972</v>
-      </c>
-      <c r="I96" t="n">
-        <v>277</v>
-      </c>
-      <c r="J96" t="n">
-        <v>15</v>
-      </c>
-      <c r="K96" t="n">
-        <v>0</v>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-11.946962</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-77.050972</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -5461,20 +6399,30 @@
           <t>NUESTRA SEÑORA DE GUADALUPE</t>
         </is>
       </c>
-      <c r="G97" t="n">
-        <v>-11.96009</v>
-      </c>
-      <c r="H97" t="n">
-        <v>-77.05316000000001</v>
-      </c>
-      <c r="I97" t="n">
-        <v>416</v>
-      </c>
-      <c r="J97" t="n">
-        <v>18</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-11.96009</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-77.05316</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -5513,20 +6461,30 @@
           <t>MATEMATICO HONORES DEL PINAR</t>
         </is>
       </c>
-      <c r="G98" t="n">
-        <v>-11.92093</v>
-      </c>
-      <c r="H98" t="n">
-        <v>-77.05871</v>
-      </c>
-      <c r="I98" t="n">
-        <v>306</v>
-      </c>
-      <c r="J98" t="n">
-        <v>26</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0</v>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-11.92093</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-77.05871</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -5565,20 +6523,30 @@
           <t>ANTON MAKARENKO</t>
         </is>
       </c>
-      <c r="G99" t="n">
-        <v>-11.91467</v>
-      </c>
-      <c r="H99" t="n">
-        <v>-77.04298</v>
-      </c>
-      <c r="I99" t="n">
-        <v>387</v>
-      </c>
-      <c r="J99" t="n">
-        <v>26</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0</v>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-11.91467</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-77.04298</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -5617,20 +6585,30 @@
           <t>SANTO TOMAS</t>
         </is>
       </c>
-      <c r="G100" t="n">
-        <v>-11.92786</v>
-      </c>
-      <c r="H100" t="n">
-        <v>-77.04616</v>
-      </c>
-      <c r="I100" t="n">
-        <v>216</v>
-      </c>
-      <c r="J100" t="n">
-        <v>10</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-11.92786</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-77.04616</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -5669,20 +6647,30 @@
           <t>SOR ANA DE LOS ANGELES</t>
         </is>
       </c>
-      <c r="G101" t="n">
-        <v>-11.9191</v>
-      </c>
-      <c r="H101" t="n">
-        <v>-77.04215000000001</v>
-      </c>
-      <c r="I101" t="n">
-        <v>231</v>
-      </c>
-      <c r="J101" t="n">
-        <v>20</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-11.9191</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-77.04215</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -5721,20 +6709,30 @@
           <t>SAN VICENTE</t>
         </is>
       </c>
-      <c r="G102" t="n">
-        <v>-11.93511</v>
-      </c>
-      <c r="H102" t="n">
-        <v>-77.05883</v>
-      </c>
-      <c r="I102" t="n">
-        <v>912</v>
-      </c>
-      <c r="J102" t="n">
-        <v>24</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-11.93511</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-77.05883</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>912</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -5773,20 +6771,30 @@
           <t>LA FE DE MARIA</t>
         </is>
       </c>
-      <c r="G103" t="n">
-        <v>-11.93455</v>
-      </c>
-      <c r="H103" t="n">
-        <v>-77.04456999999999</v>
-      </c>
-      <c r="I103" t="n">
-        <v>611</v>
-      </c>
-      <c r="J103" t="n">
-        <v>43</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-11.93455</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-77.04457</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -5825,20 +6833,30 @@
           <t>INGENIERIA DE LA ENSEÑANZA</t>
         </is>
       </c>
-      <c r="G104" t="n">
-        <v>-11.95284</v>
-      </c>
-      <c r="H104" t="n">
-        <v>-77.05338999999999</v>
-      </c>
-      <c r="I104" t="n">
-        <v>1081</v>
-      </c>
-      <c r="J104" t="n">
-        <v>20</v>
-      </c>
-      <c r="K104" t="n">
-        <v>2</v>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-11.95284</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-77.05339</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -5877,20 +6895,30 @@
           <t>JOHANNES GUTENBERG</t>
         </is>
       </c>
-      <c r="G105" t="n">
-        <v>-11.90077</v>
-      </c>
-      <c r="H105" t="n">
-        <v>-77.04648</v>
-      </c>
-      <c r="I105" t="n">
-        <v>786</v>
-      </c>
-      <c r="J105" t="n">
-        <v>48</v>
-      </c>
-      <c r="K105" t="n">
-        <v>0</v>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-11.90077</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-77.04648</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>786</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -5929,20 +6957,30 @@
           <t>CESAR VALLEJO</t>
         </is>
       </c>
-      <c r="G106" t="n">
-        <v>-11.94305</v>
-      </c>
-      <c r="H106" t="n">
-        <v>-77.04706</v>
-      </c>
-      <c r="I106" t="n">
-        <v>327</v>
-      </c>
-      <c r="J106" t="n">
-        <v>20</v>
-      </c>
-      <c r="K106" t="n">
-        <v>0</v>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-11.94305</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-77.04706</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -5981,20 +7019,30 @@
           <t>FE Y ALEGRIA 08</t>
         </is>
       </c>
-      <c r="G107" t="n">
-        <v>-11.92078</v>
-      </c>
-      <c r="H107" t="n">
-        <v>-77.03832</v>
-      </c>
-      <c r="I107" t="n">
-        <v>1148</v>
-      </c>
-      <c r="J107" t="n">
-        <v>47</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0</v>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-11.92078</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-77.03832</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1148</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -6033,20 +7081,30 @@
           <t>MARCELINO CHAMPAGNAT</t>
         </is>
       </c>
-      <c r="G108" t="n">
-        <v>-11.90925</v>
-      </c>
-      <c r="H108" t="n">
-        <v>-77.04307</v>
-      </c>
-      <c r="I108" t="n">
-        <v>237</v>
-      </c>
-      <c r="J108" t="n">
-        <v>16</v>
-      </c>
-      <c r="K108" t="n">
-        <v>0</v>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-11.90925</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-77.04307</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -6085,20 +7143,30 @@
           <t>IVAN PAVLOV</t>
         </is>
       </c>
-      <c r="G109" t="n">
-        <v>-11.92437</v>
-      </c>
-      <c r="H109" t="n">
-        <v>-77.04364</v>
-      </c>
-      <c r="I109" t="n">
-        <v>283</v>
-      </c>
-      <c r="J109" t="n">
-        <v>17</v>
-      </c>
-      <c r="K109" t="n">
-        <v>0</v>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-11.92437</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-77.04364</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -6137,20 +7205,30 @@
           <t>JESUS EL MAESTRO</t>
         </is>
       </c>
-      <c r="G110" t="n">
-        <v>-11.91621</v>
-      </c>
-      <c r="H110" t="n">
-        <v>-77.03138</v>
-      </c>
-      <c r="I110" t="n">
-        <v>260</v>
-      </c>
-      <c r="J110" t="n">
-        <v>18</v>
-      </c>
-      <c r="K110" t="n">
-        <v>0</v>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-11.91621</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-77.03138</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -6189,20 +7267,30 @@
           <t>GENES DE PRIMAVERA</t>
         </is>
       </c>
-      <c r="G111" t="n">
-        <v>-11.92765</v>
-      </c>
-      <c r="H111" t="n">
-        <v>-77.054</v>
-      </c>
-      <c r="I111" t="n">
-        <v>235</v>
-      </c>
-      <c r="J111" t="n">
-        <v>11</v>
-      </c>
-      <c r="K111" t="n">
-        <v>0</v>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-11.92765</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-77.054</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -6241,20 +7329,30 @@
           <t>FE Y ALEGRIA 11</t>
         </is>
       </c>
-      <c r="G112" t="n">
-        <v>-11.91561</v>
-      </c>
-      <c r="H112" t="n">
-        <v>-77.02516</v>
-      </c>
-      <c r="I112" t="n">
-        <v>1377</v>
-      </c>
-      <c r="J112" t="n">
-        <v>57</v>
-      </c>
-      <c r="K112" t="n">
-        <v>0</v>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-11.91561</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-77.02516</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1377</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -6293,20 +7391,30 @@
           <t>FE Y ALEGRIA 13</t>
         </is>
       </c>
-      <c r="G113" t="n">
-        <v>-11.9128</v>
-      </c>
-      <c r="H113" t="n">
-        <v>-77.0094</v>
-      </c>
-      <c r="I113" t="n">
-        <v>1745</v>
-      </c>
-      <c r="J113" t="n">
-        <v>65</v>
-      </c>
-      <c r="K113" t="n">
-        <v>0</v>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-11.9128</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-77.0094</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1745</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -6345,20 +7453,30 @@
           <t>HUSARES DE JUNIN</t>
         </is>
       </c>
-      <c r="G114" t="n">
-        <v>-11.91534</v>
-      </c>
-      <c r="H114" t="n">
-        <v>-77.01432</v>
-      </c>
-      <c r="I114" t="n">
-        <v>314</v>
-      </c>
-      <c r="J114" t="n">
-        <v>23</v>
-      </c>
-      <c r="K114" t="n">
-        <v>0</v>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-11.91534</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-77.01432</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -6397,20 +7515,30 @@
           <t>PRESENTACION DE MARIA 41</t>
         </is>
       </c>
-      <c r="G115" t="n">
-        <v>-11.95058</v>
-      </c>
-      <c r="H115" t="n">
-        <v>-77.05162</v>
-      </c>
-      <c r="I115" t="n">
-        <v>971</v>
-      </c>
-      <c r="J115" t="n">
-        <v>67</v>
-      </c>
-      <c r="K115" t="n">
-        <v>0</v>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-11.95058</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>-77.05162</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>971</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -6449,20 +7577,30 @@
           <t>JESUS OBRERO</t>
         </is>
       </c>
-      <c r="G116" t="n">
-        <v>-11.95287</v>
-      </c>
-      <c r="H116" t="n">
-        <v>-77.05253999999999</v>
-      </c>
-      <c r="I116" t="n">
-        <v>624</v>
-      </c>
-      <c r="J116" t="n">
-        <v>49</v>
-      </c>
-      <c r="K116" t="n">
-        <v>2</v>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-11.95287</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-77.05254</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -6501,20 +7639,30 @@
           <t>FE Y ALEGRIA 10</t>
         </is>
       </c>
-      <c r="G117" t="n">
-        <v>-11.91727</v>
-      </c>
-      <c r="H117" t="n">
-        <v>-77.0406</v>
-      </c>
-      <c r="I117" t="n">
-        <v>986</v>
-      </c>
-      <c r="J117" t="n">
-        <v>53</v>
-      </c>
-      <c r="K117" t="n">
-        <v>0</v>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-11.91727</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-77.0406</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -6553,20 +7701,30 @@
           <t>JESUS</t>
         </is>
       </c>
-      <c r="G118" t="n">
-        <v>-11.91625</v>
-      </c>
-      <c r="H118" t="n">
-        <v>-77.02771</v>
-      </c>
-      <c r="I118" t="n">
-        <v>234</v>
-      </c>
-      <c r="J118" t="n">
-        <v>14</v>
-      </c>
-      <c r="K118" t="n">
-        <v>0</v>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-11.91625</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>-77.02771</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -6605,20 +7763,30 @@
           <t>SARITA COLONIA</t>
         </is>
       </c>
-      <c r="G119" t="n">
-        <v>-11.92516</v>
-      </c>
-      <c r="H119" t="n">
-        <v>-77.04167</v>
-      </c>
-      <c r="I119" t="n">
-        <v>277</v>
-      </c>
-      <c r="J119" t="n">
-        <v>8</v>
-      </c>
-      <c r="K119" t="n">
-        <v>0</v>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-11.92516</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>-77.04167</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -6657,20 +7825,30 @@
           <t>JAIME WHITE</t>
         </is>
       </c>
-      <c r="G120" t="n">
-        <v>-11.936118</v>
-      </c>
-      <c r="H120" t="n">
-        <v>-77.04454200000001</v>
-      </c>
-      <c r="I120" t="n">
-        <v>333</v>
-      </c>
-      <c r="J120" t="n">
-        <v>9</v>
-      </c>
-      <c r="K120" t="n">
-        <v>0</v>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-11.936118</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-77.044542</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -6709,20 +7887,30 @@
           <t>LICEO SANTO DOMINGO</t>
         </is>
       </c>
-      <c r="G121" t="n">
-        <v>-11.91322</v>
-      </c>
-      <c r="H121" t="n">
-        <v>-77.05262999999999</v>
-      </c>
-      <c r="I121" t="n">
-        <v>2019</v>
-      </c>
-      <c r="J121" t="n">
-        <v>92</v>
-      </c>
-      <c r="K121" t="n">
-        <v>0</v>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-11.91322</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>-77.05263</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -6761,20 +7949,30 @@
           <t>SONIA AMADOR JAIME</t>
         </is>
       </c>
-      <c r="G122" t="n">
-        <v>-11.95381</v>
-      </c>
-      <c r="H122" t="n">
-        <v>-77.05101000000001</v>
-      </c>
-      <c r="I122" t="n">
-        <v>99</v>
-      </c>
-      <c r="J122" t="n">
-        <v>8</v>
-      </c>
-      <c r="K122" t="n">
-        <v>3</v>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-11.95381</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-77.05101</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -6813,20 +8011,30 @@
           <t>JACK GOLDFARB</t>
         </is>
       </c>
-      <c r="G123" t="n">
-        <v>-11.94846</v>
-      </c>
-      <c r="H123" t="n">
-        <v>-77.05007000000001</v>
-      </c>
-      <c r="I123" t="n">
-        <v>288</v>
-      </c>
-      <c r="J123" t="n">
-        <v>30</v>
-      </c>
-      <c r="K123" t="n">
-        <v>0</v>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-11.94846</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-77.05007</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -6865,20 +8073,30 @@
           <t>2079 ANTONIO RAIMONDI</t>
         </is>
       </c>
-      <c r="G124" t="n">
-        <v>-11.95251</v>
-      </c>
-      <c r="H124" t="n">
-        <v>-77.06737</v>
-      </c>
-      <c r="I124" t="n">
-        <v>926</v>
-      </c>
-      <c r="J124" t="n">
-        <v>44</v>
-      </c>
-      <c r="K124" t="n">
-        <v>0</v>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-11.95251</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>-77.06737</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -6917,20 +8135,30 @@
           <t>3024 JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
-      <c r="G125" t="n">
-        <v>-11.94278</v>
-      </c>
-      <c r="H125" t="n">
-        <v>-77.06833</v>
-      </c>
-      <c r="I125" t="n">
-        <v>998</v>
-      </c>
-      <c r="J125" t="n">
-        <v>50</v>
-      </c>
-      <c r="K125" t="n">
-        <v>0</v>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-11.94278</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>-77.06833</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -6969,20 +8197,30 @@
           <t>UNION LOS OLIVOS</t>
         </is>
       </c>
-      <c r="G126" t="n">
-        <v>-11.9476</v>
-      </c>
-      <c r="H126" t="n">
-        <v>-77.067533</v>
-      </c>
-      <c r="I126" t="n">
-        <v>304</v>
-      </c>
-      <c r="J126" t="n">
-        <v>17</v>
-      </c>
-      <c r="K126" t="n">
-        <v>0</v>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-11.9476</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>-77.067533</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -7021,20 +8259,30 @@
           <t>MI PEQUEÑO MUNDO DE SANTA LUZMILA</t>
         </is>
       </c>
-      <c r="G127" t="n">
-        <v>-11.94454</v>
-      </c>
-      <c r="H127" t="n">
-        <v>-77.06368999999999</v>
-      </c>
-      <c r="I127" t="n">
-        <v>142</v>
-      </c>
-      <c r="J127" t="n">
-        <v>9</v>
-      </c>
-      <c r="K127" t="n">
-        <v>1</v>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-11.94454</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>-77.06369</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -7073,20 +8321,30 @@
           <t>8181 HEROES DEL ALTO CENEPA</t>
         </is>
       </c>
-      <c r="G128" t="n">
-        <v>-11.92344</v>
-      </c>
-      <c r="H128" t="n">
-        <v>-77.06047</v>
-      </c>
-      <c r="I128" t="n">
-        <v>744</v>
-      </c>
-      <c r="J128" t="n">
-        <v>34</v>
-      </c>
-      <c r="K128" t="n">
-        <v>0</v>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-11.92344</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>-77.06047</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -7125,20 +8383,30 @@
           <t>BARTON DE COMAS</t>
         </is>
       </c>
-      <c r="G129" t="n">
-        <v>-11.96869</v>
-      </c>
-      <c r="H129" t="n">
-        <v>-77.06034</v>
-      </c>
-      <c r="I129" t="n">
-        <v>311</v>
-      </c>
-      <c r="J129" t="n">
-        <v>13</v>
-      </c>
-      <c r="K129" t="n">
-        <v>0</v>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-11.96869</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>-77.06034</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -7177,20 +8445,30 @@
           <t>JESUS, NUESTRO AMIGO DE LA LIBERTAD</t>
         </is>
       </c>
-      <c r="G130" t="n">
-        <v>-11.95754</v>
-      </c>
-      <c r="H130" t="n">
-        <v>-77.04913000000001</v>
-      </c>
-      <c r="I130" t="n">
-        <v>83</v>
-      </c>
-      <c r="J130" t="n">
-        <v>9</v>
-      </c>
-      <c r="K130" t="n">
-        <v>2</v>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>-11.95754</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-77.04913</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -7229,20 +8507,30 @@
           <t>NUESTRA SEÑORA DE MONSERRAT DE COMAS</t>
         </is>
       </c>
-      <c r="G131" t="n">
-        <v>-11.96929</v>
-      </c>
-      <c r="H131" t="n">
-        <v>-77.06027</v>
-      </c>
-      <c r="I131" t="n">
-        <v>339</v>
-      </c>
-      <c r="J131" t="n">
-        <v>18</v>
-      </c>
-      <c r="K131" t="n">
-        <v>0</v>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-11.96929</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>-77.06027</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -7281,20 +8569,30 @@
           <t>SONIA AMADOR JAIME II</t>
         </is>
       </c>
-      <c r="G132" t="n">
-        <v>-11.95313</v>
-      </c>
-      <c r="H132" t="n">
-        <v>-77.05052999999999</v>
-      </c>
-      <c r="I132" t="n">
-        <v>59</v>
-      </c>
-      <c r="J132" t="n">
-        <v>7</v>
-      </c>
-      <c r="K132" t="n">
-        <v>3</v>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>-11.95313</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>-77.05053</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -7333,20 +8631,30 @@
           <t>GETSEMANI</t>
         </is>
       </c>
-      <c r="G133" t="n">
-        <v>-11.91227</v>
-      </c>
-      <c r="H133" t="n">
-        <v>-77.02746999999999</v>
-      </c>
-      <c r="I133" t="n">
-        <v>228</v>
-      </c>
-      <c r="J133" t="n">
-        <v>12</v>
-      </c>
-      <c r="K133" t="n">
-        <v>0</v>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-11.91227</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>-77.02747</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -7385,20 +8693,30 @@
           <t>CRISTO RAMOS</t>
         </is>
       </c>
-      <c r="G134" t="n">
-        <v>-11.95741</v>
-      </c>
-      <c r="H134" t="n">
-        <v>-77.04122</v>
-      </c>
-      <c r="I134" t="n">
-        <v>334</v>
-      </c>
-      <c r="J134" t="n">
-        <v>16</v>
-      </c>
-      <c r="K134" t="n">
-        <v>0</v>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-11.95741</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>-77.04122</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -7437,20 +8755,30 @@
           <t>TRENTO PRO</t>
         </is>
       </c>
-      <c r="G135" t="n">
-        <v>-11.9276</v>
-      </c>
-      <c r="H135" t="n">
-        <v>-77.07216</v>
-      </c>
-      <c r="I135" t="n">
-        <v>316</v>
-      </c>
-      <c r="J135" t="n">
-        <v>19</v>
-      </c>
-      <c r="K135" t="n">
-        <v>0</v>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-11.9276</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-77.07216</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -7489,20 +8817,30 @@
           <t>BERNE</t>
         </is>
       </c>
-      <c r="G136" t="n">
-        <v>-11.95314</v>
-      </c>
-      <c r="H136" t="n">
-        <v>-77.05289999999999</v>
-      </c>
-      <c r="I136" t="n">
-        <v>76</v>
-      </c>
-      <c r="J136" t="n">
-        <v>10</v>
-      </c>
-      <c r="K136" t="n">
-        <v>2</v>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-11.95314</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-77.0529</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -7541,20 +8879,30 @@
           <t>MOM'S SCHOOL KINDERGARDEN</t>
         </is>
       </c>
-      <c r="G137" t="n">
-        <v>-11.936886</v>
-      </c>
-      <c r="H137" t="n">
-        <v>-77.047864</v>
-      </c>
-      <c r="I137" t="n">
-        <v>44</v>
-      </c>
-      <c r="J137" t="n">
-        <v>4</v>
-      </c>
-      <c r="K137" t="n">
-        <v>2</v>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-11.936886</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>-77.047864</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -7593,20 +8941,30 @@
           <t>SANTA BEATRIZ</t>
         </is>
       </c>
-      <c r="G138" t="n">
-        <v>-11.9466</v>
-      </c>
-      <c r="H138" t="n">
-        <v>-77.0681</v>
-      </c>
-      <c r="I138" t="n">
-        <v>247</v>
-      </c>
-      <c r="J138" t="n">
-        <v>11</v>
-      </c>
-      <c r="K138" t="n">
-        <v>0</v>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-11.9466</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-77.0681</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -7645,20 +9003,30 @@
           <t>HOWARD GARDNER DE LIMA NORTE</t>
         </is>
       </c>
-      <c r="G139" t="n">
-        <v>-11.95384</v>
-      </c>
-      <c r="H139" t="n">
-        <v>-77.05766</v>
-      </c>
-      <c r="I139" t="n">
-        <v>238</v>
-      </c>
-      <c r="J139" t="n">
-        <v>19</v>
-      </c>
-      <c r="K139" t="n">
-        <v>0</v>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-11.95384</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-77.05766</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -7697,20 +9065,30 @@
           <t>NUESTRA SEÑORA DE GUADALUPE SEGUNDO</t>
         </is>
       </c>
-      <c r="G140" t="n">
-        <v>-11.95863</v>
-      </c>
-      <c r="H140" t="n">
-        <v>-77.05249999999999</v>
-      </c>
-      <c r="I140" t="n">
-        <v>277</v>
-      </c>
-      <c r="J140" t="n">
-        <v>15</v>
-      </c>
-      <c r="K140" t="n">
-        <v>0</v>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>-11.95863</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-77.0525</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -7749,20 +9127,30 @@
           <t>SANTA MARIA LA REINA</t>
         </is>
       </c>
-      <c r="G141" t="n">
-        <v>-11.914505</v>
-      </c>
-      <c r="H141" t="n">
-        <v>-77.03518800000001</v>
-      </c>
-      <c r="I141" t="n">
-        <v>277</v>
-      </c>
-      <c r="J141" t="n">
-        <v>5</v>
-      </c>
-      <c r="K141" t="n">
-        <v>0</v>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>-11.914505</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>-77.035188</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -7801,20 +9189,30 @@
           <t>CANTOR COLLEGE</t>
         </is>
       </c>
-      <c r="G142" t="n">
-        <v>-11.96568</v>
-      </c>
-      <c r="H142" t="n">
-        <v>-77.06135</v>
-      </c>
-      <c r="I142" t="n">
-        <v>318</v>
-      </c>
-      <c r="J142" t="n">
-        <v>24</v>
-      </c>
-      <c r="K142" t="n">
-        <v>0</v>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-11.96568</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>-77.06135</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -7853,20 +9251,30 @@
           <t>GENES EL PINAR - COMAS</t>
         </is>
       </c>
-      <c r="G143" t="n">
-        <v>-11.9158</v>
-      </c>
-      <c r="H143" t="n">
-        <v>-77.04904000000001</v>
-      </c>
-      <c r="I143" t="n">
-        <v>203</v>
-      </c>
-      <c r="J143" t="n">
-        <v>14</v>
-      </c>
-      <c r="K143" t="n">
-        <v>0</v>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>-11.9158</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>-77.04904</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -7905,20 +9313,30 @@
           <t>TRILCE DE COMAS</t>
         </is>
       </c>
-      <c r="G144" t="n">
-        <v>-11.95351</v>
-      </c>
-      <c r="H144" t="n">
-        <v>-77.05374</v>
-      </c>
-      <c r="I144" t="n">
-        <v>797</v>
-      </c>
-      <c r="J144" t="n">
-        <v>10</v>
-      </c>
-      <c r="K144" t="n">
-        <v>1</v>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>-11.95351</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-77.05374</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>797</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -7957,20 +9375,30 @@
           <t>JESUS ANGELES</t>
         </is>
       </c>
-      <c r="G145" t="n">
-        <v>-11.94049</v>
-      </c>
-      <c r="H145" t="n">
-        <v>-77.06656</v>
-      </c>
-      <c r="I145" t="n">
-        <v>56</v>
-      </c>
-      <c r="J145" t="n">
-        <v>3</v>
-      </c>
-      <c r="K145" t="n">
-        <v>1</v>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-11.94049</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>-77.06656</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -8009,20 +9437,30 @@
           <t>DELTA</t>
         </is>
       </c>
-      <c r="G146" t="n">
-        <v>-11.9053</v>
-      </c>
-      <c r="H146" t="n">
-        <v>-77.04044</v>
-      </c>
-      <c r="I146" t="n">
-        <v>7</v>
-      </c>
-      <c r="J146" t="n">
-        <v>5</v>
-      </c>
-      <c r="K146" t="n">
-        <v>1</v>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>-11.9053</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>-77.04044</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -8061,20 +9499,30 @@
           <t>MARIA DEL ANGEL</t>
         </is>
       </c>
-      <c r="G147" t="n">
-        <v>-11.95204</v>
-      </c>
-      <c r="H147" t="n">
-        <v>-77.05456</v>
-      </c>
-      <c r="I147" t="n">
-        <v>238</v>
-      </c>
-      <c r="J147" t="n">
-        <v>18</v>
-      </c>
-      <c r="K147" t="n">
-        <v>0</v>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-11.95204</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>-77.05456</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -8113,20 +9561,30 @@
           <t>BILINGUE FEDERICO VILLARREAL / FEDERICO VILLARREAL - BILINGÜE</t>
         </is>
       </c>
-      <c r="G148" t="n">
-        <v>-11.95837</v>
-      </c>
-      <c r="H148" t="n">
-        <v>-77.05256</v>
-      </c>
-      <c r="I148" t="n">
-        <v>234</v>
-      </c>
-      <c r="J148" t="n">
-        <v>16</v>
-      </c>
-      <c r="K148" t="n">
-        <v>0</v>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>-11.95837</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>-77.05256</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -8165,20 +9623,30 @@
           <t>TRILCE LAS VEGAS</t>
         </is>
       </c>
-      <c r="G149" t="n">
-        <v>-11.95344</v>
-      </c>
-      <c r="H149" t="n">
-        <v>-77.05956999999999</v>
-      </c>
-      <c r="I149" t="n">
-        <v>271</v>
-      </c>
-      <c r="J149" t="n">
-        <v>12</v>
-      </c>
-      <c r="K149" t="n">
-        <v>0</v>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-11.95344</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>-77.05957</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -8217,20 +9685,30 @@
           <t>ALFA COMAS</t>
         </is>
       </c>
-      <c r="G150" t="n">
-        <v>-11.94338</v>
-      </c>
-      <c r="H150" t="n">
-        <v>-77.06514</v>
-      </c>
-      <c r="I150" t="n">
-        <v>234</v>
-      </c>
-      <c r="J150" t="n">
-        <v>21</v>
-      </c>
-      <c r="K150" t="n">
-        <v>0</v>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-11.94338</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>-77.06514</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -8269,20 +9747,30 @@
           <t>AL GORE</t>
         </is>
       </c>
-      <c r="G151" t="n">
-        <v>-11.948187</v>
-      </c>
-      <c r="H151" t="n">
-        <v>-77.050972</v>
-      </c>
-      <c r="I151" t="n">
-        <v>341</v>
-      </c>
-      <c r="J151" t="n">
-        <v>26</v>
-      </c>
-      <c r="K151" t="n">
-        <v>0</v>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>-11.948187</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>-77.050972</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -8321,20 +9809,30 @@
           <t>TECHNOLOGY SCHOOLS DEL RETABLO I</t>
         </is>
       </c>
-      <c r="G152" t="n">
-        <v>-11.93572</v>
-      </c>
-      <c r="H152" t="n">
-        <v>-77.05902</v>
-      </c>
-      <c r="I152" t="n">
-        <v>1320</v>
-      </c>
-      <c r="J152" t="n">
-        <v>55</v>
-      </c>
-      <c r="K152" t="n">
-        <v>0</v>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>-11.93572</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>-77.05902</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -8373,20 +9871,30 @@
           <t>MIGUEL ANGEL ASTURIAS DE CARABAYLLO</t>
         </is>
       </c>
-      <c r="G153" t="n">
-        <v>-11.91529</v>
-      </c>
-      <c r="H153" t="n">
-        <v>-77.0266</v>
-      </c>
-      <c r="I153" t="n">
-        <v>460</v>
-      </c>
-      <c r="J153" t="n">
-        <v>14</v>
-      </c>
-      <c r="K153" t="n">
-        <v>0</v>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>-11.91529</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>-77.0266</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -8425,20 +9933,30 @@
           <t>SANTO TOMAS</t>
         </is>
       </c>
-      <c r="G154" t="n">
-        <v>-11.92611</v>
-      </c>
-      <c r="H154" t="n">
-        <v>-77.04322000000001</v>
-      </c>
-      <c r="I154" t="n">
-        <v>125</v>
-      </c>
-      <c r="J154" t="n">
-        <v>10</v>
-      </c>
-      <c r="K154" t="n">
-        <v>1</v>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-11.92611</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>-77.04322</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -8477,20 +9995,30 @@
           <t>SACO OLIVEROS EL RETABLO</t>
         </is>
       </c>
-      <c r="G155" t="n">
-        <v>-11.93601</v>
-      </c>
-      <c r="H155" t="n">
-        <v>-77.0582</v>
-      </c>
-      <c r="I155" t="n">
-        <v>572</v>
-      </c>
-      <c r="J155" t="n">
-        <v>34</v>
-      </c>
-      <c r="K155" t="n">
-        <v>0</v>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>-11.93601</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>-77.0582</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -8529,20 +10057,30 @@
           <t>MARIA MONTESSORI STOPPIANI / NUEVO MONTESSORI II</t>
         </is>
       </c>
-      <c r="G156" t="n">
-        <v>-11.911136</v>
-      </c>
-      <c r="H156" t="n">
-        <v>-77.022336</v>
-      </c>
-      <c r="I156" t="n">
-        <v>545</v>
-      </c>
-      <c r="J156" t="n">
-        <v>14</v>
-      </c>
-      <c r="K156" t="n">
-        <v>0</v>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-11.911136</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>-77.022336</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -8581,20 +10119,30 @@
           <t>MARIA MEDALLA MILAGROSA</t>
         </is>
       </c>
-      <c r="G157" t="n">
-        <v>-11.906485</v>
-      </c>
-      <c r="H157" t="n">
-        <v>-77.05296</v>
-      </c>
-      <c r="I157" t="n">
-        <v>430</v>
-      </c>
-      <c r="J157" t="n">
-        <v>32</v>
-      </c>
-      <c r="K157" t="n">
-        <v>0</v>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>-11.906485</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>-77.05296</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -8633,20 +10181,30 @@
           <t>IVAN PAVLOV</t>
         </is>
       </c>
-      <c r="G158" t="n">
-        <v>-11.921756</v>
-      </c>
-      <c r="H158" t="n">
-        <v>-77.043063</v>
-      </c>
-      <c r="I158" t="n">
-        <v>67</v>
-      </c>
-      <c r="J158" t="n">
-        <v>4</v>
-      </c>
-      <c r="K158" t="n">
-        <v>1</v>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>-11.921756</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>-77.043063</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -8685,20 +10243,30 @@
           <t>PROLOG DE COMAS</t>
         </is>
       </c>
-      <c r="G159" t="n">
-        <v>-11.94369</v>
-      </c>
-      <c r="H159" t="n">
-        <v>-77.05001</v>
-      </c>
-      <c r="I159" t="n">
-        <v>219</v>
-      </c>
-      <c r="J159" t="n">
-        <v>33</v>
-      </c>
-      <c r="K159" t="n">
-        <v>0</v>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-11.94369</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>-77.05001</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LIMA-LIMA-COMAS.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-COMAS.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14945</t>
+          <t>301003</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ANGELITOS DE SANTA MARIA</t>
+          <t>354 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-11.91243</t>
+          <t>-11.92742</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.02597</t>
+          <t>-77.056</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>167</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>230713</t>
+          <t>301022</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MARIO VARGAS LLOSA</t>
+          <t>369</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.92458</t>
+          <t>-11.93322</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.05362</t>
+          <t>-77.05404</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>240</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>300876</t>
+          <t>301036</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LA PASCANA</t>
+          <t>370 VIRGEN DE LA PUERTA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.93643</t>
+          <t>-11.95692</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.04637</t>
+          <t>-77.03582</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>241</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>300881</t>
+          <t>301041</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SANGARARA</t>
+          <t>373</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-11.915543</t>
+          <t>-11.95157</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.055633</t>
+          <t>-77.0574</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>216</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>300895</t>
+          <t>302762</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LUIS ENRIQUE XIV</t>
+          <t>SANTO TOMAS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.9141</t>
+          <t>-11.92786</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.0112</t>
+          <t>-77.04616</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>216</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>300918</t>
+          <t>605245</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>BERNE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.9662</t>
+          <t>-11.95314</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.05441</t>
+          <t>-77.0529</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>300937</t>
+          <t>710944</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>TRILCE DE COMAS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.92047</t>
+          <t>-11.95351</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.04411</t>
+          <t>-77.05374</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>797</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>300956</t>
+          <t>823168</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>326 MARIA MONTESSORI</t>
+          <t>SANTO TOMAS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.95697</t>
+          <t>-11.92611</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.05621</t>
+          <t>-77.04322</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>125</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>300961</t>
+          <t>14945</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>ANGELITOS DE SANTA MARIA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-11.94098</t>
+          <t>-11.91243</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.06309</t>
+          <t>-77.02597</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>300975</t>
+          <t>300918</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>337 SANGARARA</t>
+          <t>03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-11.92474</t>
+          <t>-11.9662</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.04515</t>
+          <t>-77.05441</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>209</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,27 +1121,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>300980</t>
+          <t>300937</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>341 EL RETABLO</t>
+          <t>317</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.93803</t>
+          <t>-11.92047</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.05577</t>
+          <t>-77.04411</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>237</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1183,37 +1183,37 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>301003</t>
+          <t>300980</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>354 NUESTRA SEÑORA DE FATIMA</t>
+          <t>341 EL RETABLO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.92742</t>
+          <t>-11.93803</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.056</t>
+          <t>-77.05577</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>301022</t>
+          <t>301102</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>868</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-11.93322</t>
+          <t>-11.9098</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.05404</t>
+          <t>-77.04598</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>301036</t>
+          <t>301197</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>370 VIRGEN DE LA PUERTA</t>
+          <t>054</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-11.95692</t>
+          <t>-11.959535</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.03582</t>
+          <t>-77.04419</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>362</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,37 +1431,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>301041</t>
+          <t>301201</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>316 SAN FELIPE</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-11.95157</t>
+          <t>-11.90046</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.0574</t>
+          <t>-77.04003</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>264</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1493,27 +1493,27 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>301102</t>
+          <t>302026</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.9098</t>
+          <t>-11.92054</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.04598</t>
+          <t>-77.03962</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>274</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>301116</t>
+          <t>303549</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CARMEN ALTO</t>
+          <t>GENES DE PRIMAVERA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-11.94631</t>
+          <t>-11.92765</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.03114</t>
+          <t>-77.054</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>235</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>301121</t>
+          <t>625309</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>888 SEÑOR DE LOS MILAGROS</t>
+          <t>SANTA BEATRIZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-11.91563</t>
+          <t>-11.9466</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.03456</t>
+          <t>-77.0681</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>247</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>301135</t>
+          <t>564424</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>LUIS ENRIQUE II</t>
+          <t>GETSEMANI</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-11.91925</t>
+          <t>-11.91227</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.03833</t>
+          <t>-77.02747</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>228</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>301140</t>
+          <t>712387</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>LUIS ENRIQUE XIII</t>
+          <t>TRILCE LAS VEGAS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-11.90842</t>
+          <t>-11.95344</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.04148</t>
+          <t>-77.05957</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>271</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>301159</t>
+          <t>300956</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>326 MARIA MONTESSORI</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-11.94334</t>
+          <t>-11.95697</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.05569</t>
+          <t>-77.05621</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>296</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>301164</t>
+          <t>301215</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>368 ANGELITOS DE JESUS</t>
+          <t>328</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-11.91963</t>
+          <t>-11.90765</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.05964</t>
+          <t>-77.03788</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>284</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>301178</t>
+          <t>514740</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>02 JOSE GALVITO</t>
+          <t>BARTON DE COMAS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-11.911038</t>
+          <t>-11.96869</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.012883</t>
+          <t>-77.06034</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>311</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>301183</t>
+          <t>300975</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>337 SANGARARA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-11.9381</t>
+          <t>-11.92474</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.04256</t>
+          <t>-77.04515</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>265</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>301197</t>
+          <t>301116</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>CARMEN ALTO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-11.959535</t>
+          <t>-11.94631</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.04419</t>
+          <t>-77.03114</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>304</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,37 +2113,37 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>301201</t>
+          <t>301319</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>316 SAN FELIPE</t>
+          <t>2035 FERNANDO BELAUNDE TERRY</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-11.90046</t>
+          <t>-11.94199</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.04003</t>
+          <t>-77.03513</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>368</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>301215</t>
+          <t>301480</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-11.90765</t>
+          <t>-11.96378</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.03788</t>
+          <t>-77.06124</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>340</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>301258</t>
+          <t>301574</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>8156 PERUANO ALEMAN</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-11.93058</t>
+          <t>-11.90871</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.05648</t>
+          <t>-77.04278</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>309</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>301277</t>
+          <t>303771</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2016 FRANCISCO BOLOGNESI</t>
+          <t>JESUS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-11.94477</t>
+          <t>-11.91625</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.05477</t>
+          <t>-77.02771</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>234</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>301282</t>
+          <t>710562</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2020 MAESTRO JOSE ANTONIO ENCINAS</t>
+          <t>GENES EL PINAR - COMAS</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-11.93864</t>
+          <t>-11.9158</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.05562</t>
+          <t>-77.04904</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>203</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>301300</t>
+          <t>812037</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2033 NUESTRA SEÑORA DE FATIMA</t>
+          <t>MIGUEL ANGEL ASTURIAS DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-11.95544</t>
+          <t>-11.91529</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-77.05324</t>
+          <t>-77.0266</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>460</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2485,27 +2485,27 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>301319</t>
+          <t>851458</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2035 FERNANDO BELAUNDE TERRY</t>
+          <t>MARIA MONTESSORI STOPPIANI / NUEVO MONTESSORI II</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-11.94199</t>
+          <t>-11.911136</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.03513</t>
+          <t>-77.022336</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>545</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>301324</t>
+          <t>300881</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2042 FRAY MARTIN DE PORRES</t>
+          <t>SANGARARA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-11.96187</t>
+          <t>-11.915543</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.04706</t>
+          <t>-77.055633</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>336</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>301338</t>
+          <t>300961</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2043 SANGARARA</t>
+          <t>334</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-11.91968</t>
+          <t>-11.94098</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.0442</t>
+          <t>-77.06309</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>348</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>301357</t>
+          <t>301164</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2046 VIRGEN DE LAS MERCEDES</t>
+          <t>368 ANGELITOS DE JESUS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-11.97198</t>
+          <t>-11.91963</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.05695</t>
+          <t>-77.05964</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>388</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>301376</t>
+          <t>301404</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2055 PRIMERO DE ABRIL</t>
+          <t>2072 LEV SEMIONOVICH VIGOTSKI</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-11.91554</t>
+          <t>-11.90473</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-77.04418</t>
+          <t>-77.05477</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>354</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>301381</t>
+          <t>301550</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2059 SUECIA</t>
+          <t>3085 PEDRO VILCA APAZA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-11.92514</t>
+          <t>-11.95164</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-77.03878</t>
+          <t>-77.05717</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>389</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>301395</t>
+          <t>302229</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>LA SEMILLITA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-11.91124</t>
+          <t>-11.95989</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-77.01776</t>
+          <t>-77.04742</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>251</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,27 +2919,27 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>301404</t>
+          <t>302253</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2072 LEV SEMIONOVICH VIGOTSKI</t>
+          <t>PAUL GROUSSAC DE HUAQUILLAY</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-11.90473</t>
+          <t>-11.946962</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-77.05477</t>
+          <t>-77.050972</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>277</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>301418</t>
+          <t>708880</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2077 SAN MARTIN DE PORRES DE AÑO NUEVO / SAN MARTIN DE PORRES</t>
+          <t>NUESTRA SEÑORA DE GUADALUPE SEGUNDO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-11.92842</t>
+          <t>-11.95863</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-77.04119</t>
+          <t>-77.0525</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>277</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>301423</t>
+          <t>301135</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>LUIS ENRIQUE II</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-11.90724</t>
+          <t>-11.91925</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-77.03831</t>
+          <t>-77.03833</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>301437</t>
+          <t>302012</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2100 JUAN VELASCO ALVARADO</t>
+          <t>LUIS ENRIQUE XVII</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-11.95464</t>
+          <t>-11.93585</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-77.05504</t>
+          <t>-77.05155</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>381</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>301442</t>
+          <t>303262</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>3060 ALFONSO UGARTE VERNAL</t>
+          <t>MARCELINO CHAMPAGNAT</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-11.93905</t>
+          <t>-11.90925</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-77.05315</t>
+          <t>-77.04307</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>237</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>301456</t>
+          <t>582461</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>3062 SANTA ROSA</t>
+          <t>CRISTO RAMOS</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-11.94918</t>
+          <t>-11.95741</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-77.0486</t>
+          <t>-77.04122</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>334</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>301461</t>
+          <t>711854</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>BILINGUE FEDERICO VILLARREAL / FEDERICO VILLARREAL - BILINGÜE</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-11.94199</t>
+          <t>-11.95837</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-77.04259</t>
+          <t>-77.05256</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>234</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>301475</t>
+          <t>300895</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>8160 LOS CHASQUIS</t>
+          <t>LUIS ENRIQUE XIV</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-11.93434</t>
+          <t>-11.9141</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-77.06114</t>
+          <t>-77.0112</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>290</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>301480</t>
+          <t>301121</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>888 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-11.96378</t>
+          <t>-11.91563</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-77.06124</t>
+          <t>-77.03456</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>331</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>301499</t>
+          <t>301140</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>LUIS ENRIQUE XIII</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-11.95767</t>
+          <t>-11.90842</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-77.04014</t>
+          <t>-77.04148</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>275</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>301512</t>
+          <t>301159</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>3072 AUGUSTO SALAZAR BONDY</t>
+          <t>371</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-11.94652</t>
+          <t>-11.94334</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-77.06183</t>
+          <t>-77.05569</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>312</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>301526</t>
+          <t>301965</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>3077 EL ALAMO</t>
+          <t>SANTA LUZMILA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-11.93319</t>
+          <t>-11.945741</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-77.06758</t>
+          <t>-77.059053</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>365</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>301531</t>
+          <t>303399</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>3082 SEÑOR DE LOS MILAGROS</t>
+          <t>IVAN PAVLOV</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-11.965354</t>
+          <t>-11.92437</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-77.059168</t>
+          <t>-77.04364</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>283</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>301550</t>
+          <t>336427</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>3085 PEDRO VILCA APAZA</t>
+          <t>UNION LOS OLIVOS</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-11.95164</t>
+          <t>-11.9476</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-77.05717</t>
+          <t>-77.067533</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>304</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>301574</t>
+          <t>230713</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>8156 PERUANO ALEMAN</t>
+          <t>MARIO VARGAS LLOSA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-11.90871</t>
+          <t>-11.92458</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-77.04278</t>
+          <t>-77.05362</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>255</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>301588</t>
+          <t>301183</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>8157 REPUBLICA DE FRANCIA</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-11.91219</t>
+          <t>-11.9381</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-77.04131</t>
+          <t>-77.04256</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>379</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>301593</t>
+          <t>302309</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>8158 ISABEL FLORES DE OLIVA</t>
+          <t>NUESTRA SEÑORA DE GUADALUPE</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-11.91616</t>
+          <t>-11.96009</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-77.050005</t>
+          <t>-77.05316</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>416</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>301606</t>
+          <t>303417</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>8173 SANTA ISOLINA</t>
+          <t>JESUS EL MAESTRO</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-11.95911</t>
+          <t>-11.91621</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-77.06226</t>
+          <t>-77.03138</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>260</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>301611</t>
+          <t>534390</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2022 SINCHI ROCA</t>
+          <t>NUESTRA SEÑORA DE MONSERRAT DE COMAS</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-11.93045</t>
+          <t>-11.96929</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-77.04964</t>
+          <t>-77.06027</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>339</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>301625</t>
+          <t>711712</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2048 JOSE CARLOS MARIATEGUI</t>
+          <t>MARIA DEL ANGEL</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-11.939926</t>
+          <t>-11.95204</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-77.063361</t>
+          <t>-77.05456</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>301630</t>
+          <t>301357</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>3055 TUPAC AMARU</t>
+          <t>2046 VIRGEN DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-11.93503</t>
+          <t>-11.97198</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-77.04317</t>
+          <t>-77.05695</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>432</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>301649</t>
+          <t>301606</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ESTADOS UNIDOS</t>
+          <t>8173 SANTA ISOLINA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-11.965191</t>
+          <t>-11.95911</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-77.05676</t>
+          <t>-77.06226</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>446</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>301668</t>
+          <t>301908</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2075 CRISTO HIJO DE DIOS</t>
+          <t>SAN CARLOS</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-11.92201</t>
+          <t>-11.90316</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-77.02409</t>
+          <t>-77.04262</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>375</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>301687</t>
+          <t>597113</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>PERU-HOLANDA</t>
+          <t>TRENTO PRO</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-11.91663</t>
+          <t>-11.9276</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-77.03561</t>
+          <t>-77.07216</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1745</t>
+          <t>316</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>301692</t>
+          <t>655155</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>LIBERTAD</t>
+          <t>HOWARD GARDNER DE LIMA NORTE</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-11.9224</t>
+          <t>-11.95384</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-77.03899</t>
+          <t>-77.05766</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,42 +4469,42 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>301705</t>
+          <t>302111</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026 SIMON BOLIVAR</t>
+          <t>ESPIRITU SANTO</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-11.95063</t>
+          <t>-11.93762</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-77.06313</t>
+          <t>-77.05025</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>301710</t>
+          <t>302818</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>3061 JORGE CHAVEZ DARTNELL</t>
+          <t>SOR ANA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-11.95925</t>
+          <t>-11.9191</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-77.0521</t>
+          <t>-77.04215</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>231</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,37 +4593,37 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>301729</t>
+          <t>302917</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>3076 SANTA ROSA</t>
+          <t>INGENIERIA DE LA ENSEÑANZA</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-11.91084</t>
+          <t>-11.95284</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-77.00576</t>
+          <t>-77.05339</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>301734</t>
+          <t>302998</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>8170 CESAR VALLEJO</t>
+          <t>CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-11.93162</t>
+          <t>-11.94305</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-77.03668</t>
+          <t>-77.04706</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>327</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>301748</t>
+          <t>301526</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>3047 REPUBLICA DE CANADA</t>
+          <t>3077 EL ALAMO</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-11.95916</t>
+          <t>-11.93319</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-77.04107</t>
+          <t>-77.06758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>508</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>301753</t>
+          <t>301588</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>3065 VIRGEN DEL CARMEN</t>
+          <t>8157 REPUBLICA DE FRANCIA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-11.93866</t>
+          <t>-11.91219</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-77.04106</t>
+          <t>-77.04131</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>522</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>301767</t>
+          <t>744878</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>3066 SEÑOR DE LOS MILAGROS</t>
+          <t>ALFA COMAS</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-11.94171</t>
+          <t>-11.94338</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-77.04826</t>
+          <t>-77.06514</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>234</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>301772</t>
+          <t>300876</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2085 SAN AGUSTIN</t>
+          <t>LA PASCANA</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-11.9323</t>
+          <t>-11.93643</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-77.05056</t>
+          <t>-77.04637</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>390</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>301786</t>
+          <t>301324</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>3096 FRANZ TAMAYO SOLARES</t>
+          <t>2042 FRAY MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-11.92383</t>
+          <t>-11.96187</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-77.05296</t>
+          <t>-77.04706</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>511</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>301791</t>
+          <t>301512</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CORONEL JOSE GALVEZ</t>
+          <t>3072 AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-11.91142</t>
+          <t>-11.94652</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-77.01487</t>
+          <t>-77.06183</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>732</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>301809</t>
+          <t>301258</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2038 INCA GARCILASO DE LA VEGA</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-11.917908</t>
+          <t>-11.93058</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-77.029028</t>
+          <t>-77.05648</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>678</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>301814</t>
+          <t>301277</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2031 JOSE VALVERDE CARO</t>
+          <t>2016 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-11.94512</t>
+          <t>-11.94477</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-77.03126</t>
+          <t>-77.05477</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>482</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>301828</t>
+          <t>301442</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>JOSE MARTI</t>
+          <t>3060 ALFONSO UGARTE VERNAL</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-11.95403</t>
+          <t>-11.93905</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-77.05587</t>
+          <t>-77.05315</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>557</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5275,37 +5275,37 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>301833</t>
+          <t>301970</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RAMON CASTILLA</t>
+          <t>3068 SAN JUDAS TADEO</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-11.93282</t>
+          <t>-11.95762</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-77.05559</t>
+          <t>-77.05009</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>473</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>301847</t>
+          <t>303667</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>EL AMAUTA</t>
+          <t>HUSARES DE JUNIN</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-11.92998</t>
+          <t>-11.91534</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-77.06647</t>
+          <t>-77.01432</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>314</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>301866</t>
+          <t>301593</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>JUAN PABLO VIZCARDO Y GUZMAN</t>
+          <t>8158 ISABEL FLORES DE OLIVA</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-11.92554</t>
+          <t>-11.91616</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-77.04526</t>
+          <t>-77.050005</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>503</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>301871</t>
+          <t>301734</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>MARISCAL ANDRES AVELINO CACERES DORREGARAY</t>
+          <t>8170 CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-11.91639</t>
+          <t>-11.93162</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-77.03376</t>
+          <t>-77.03668</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>419</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>301885</t>
+          <t>302842</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>LA ALBORADA FRANCESA</t>
+          <t>SAN VICENTE</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-11.9123</t>
+          <t>-11.93511</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-77.04734</t>
+          <t>-77.05883</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>912</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>301890</t>
+          <t>710232</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>PERUANO SUIZO</t>
+          <t>CANTOR COLLEGE</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-11.96703</t>
+          <t>-11.96568</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-77.06011</t>
+          <t>-77.06135</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>318</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>301908</t>
+          <t>301300</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>SAN CARLOS</t>
+          <t>2033 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-11.90316</t>
+          <t>-11.95544</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-77.04262</t>
+          <t>-77.05324</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>604</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>301913</t>
+          <t>301338</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SAN FELIPE</t>
+          <t>2043 SANGARARA</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-11.89896</t>
+          <t>-11.91968</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-77.04063</t>
+          <t>-77.0442</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>570</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>301927</t>
+          <t>302050</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>COMERCIO 62 ALMIRANTE MIGUEL GRAU</t>
+          <t>8186 MARIA JESUS ESPINOZA MATOS</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-11.93902</t>
+          <t>-11.89907</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-77.05314</t>
+          <t>-77.04858</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>550</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5833,37 +5833,37 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>301932</t>
+          <t>301282</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CARLOS WIESSE</t>
+          <t>2020 MAESTRO JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-11.9519</t>
+          <t>-11.93864</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-77.0505</t>
+          <t>-77.05562</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>639</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>301965</t>
+          <t>301866</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>SANTA LUZMILA</t>
+          <t>JUAN PABLO VIZCARDO Y GUZMAN</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-11.945741</t>
+          <t>-11.92554</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-77.059053</t>
+          <t>-77.04526</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>354</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5957,37 +5957,37 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>301970</t>
+          <t>302333</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>3068 SAN JUDAS TADEO</t>
+          <t>MATEMATICO HONORES DEL PINAR</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-11.95762</t>
+          <t>-11.92093</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-77.05009</t>
+          <t>-77.05871</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>306</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6019,32 +6019,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>302012</t>
+          <t>302724</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>LUIS ENRIQUE XVII</t>
+          <t>ANTON MAKARENKO</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-11.93585</t>
+          <t>-11.91467</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-77.05155</t>
+          <t>-77.04298</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>387</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6081,32 +6081,32 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>302026</t>
+          <t>745552</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>AL GORE</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-11.92054</t>
+          <t>-11.948187</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-77.03962</t>
+          <t>-77.050972</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>341</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6143,32 +6143,32 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>302050</t>
+          <t>301423</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>8186 MARIA JESUS ESPINOZA MATOS</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-11.89907</t>
+          <t>-11.90724</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-77.04858</t>
+          <t>-77.03831</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>681</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6205,37 +6205,37 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>302111</t>
+          <t>301437</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ESPIRITU SANTO</t>
+          <t>2100 JUAN VELASCO ALVARADO</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-11.93762</t>
+          <t>-11.95464</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-77.05025</t>
+          <t>-77.05504</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>661</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>302229</t>
+          <t>301461</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>LA SEMILLITA</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-11.95989</t>
+          <t>-11.94199</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-77.04742</t>
+          <t>-77.04259</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>709</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6329,37 +6329,37 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>302253</t>
+          <t>711019</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>PAUL GROUSSAC DE HUAQUILLAY</t>
+          <t>JESUS ANGELES</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-11.946962</t>
+          <t>-11.94049</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-77.050972</t>
+          <t>-77.06656</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>302309</t>
+          <t>301499</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE GUADALUPE</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-11.96009</t>
+          <t>-11.95767</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-77.05316</t>
+          <t>-77.04014</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>571</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>302333</t>
+          <t>304501</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>MATEMATICO HONORES DEL PINAR</t>
+          <t>JACK GOLDFARB</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-11.92093</t>
+          <t>-11.94846</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-77.05871</t>
+          <t>-77.05007</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>288</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6515,32 +6515,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>302724</t>
+          <t>301381</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ANTON MAKARENKO</t>
+          <t>2059 SUECIA</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-11.91467</t>
+          <t>-11.92514</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-77.04298</t>
+          <t>-77.03878</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>659</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6577,32 +6577,32 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>302762</t>
+          <t>301710</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>SANTO TOMAS</t>
+          <t>3061 JORGE CHAVEZ DARTNELL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-11.92786</t>
+          <t>-11.95925</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-77.04616</t>
+          <t>-77.0521</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>665</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>302818</t>
+          <t>301828</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SOR ANA DE LOS ANGELES</t>
+          <t>JOSE MARTI</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-11.9191</t>
+          <t>-11.95403</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-77.04215</t>
+          <t>-77.05587</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>711</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6701,32 +6701,32 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>302842</t>
+          <t>862169</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>SAN VICENTE</t>
+          <t>MARIA MEDALLA MILAGROSA</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-11.93511</t>
+          <t>-11.906485</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-77.05883</t>
+          <t>-77.05296</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>430</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6763,32 +6763,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>302903</t>
+          <t>301376</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>LA FE DE MARIA</t>
+          <t>2055 PRIMERO DE ABRIL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-11.93455</t>
+          <t>-11.91554</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-77.04457</t>
+          <t>-77.04418</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>670</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6825,42 +6825,42 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>302917</t>
+          <t>301809</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>INGENIERIA DE LA ENSEÑANZA</t>
+          <t>2038 INCA GARCILASO DE LA VEGA</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-11.95284</t>
+          <t>-11.917908</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-77.05339</t>
+          <t>-77.029028</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6887,32 +6887,32 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>302922</t>
+          <t>903419</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>JOHANNES GUTENBERG</t>
+          <t>PROLOG DE COMAS</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-11.90077</t>
+          <t>-11.94369</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>-77.04648</t>
+          <t>-77.05001</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>219</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6949,32 +6949,32 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>302998</t>
+          <t>506194</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO</t>
+          <t>8181 HEROES DEL ALTO CENEPA</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-11.94305</t>
+          <t>-11.92344</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>-77.04706</t>
+          <t>-77.06047</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>744</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7011,32 +7011,32 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>303064</t>
+          <t>826807</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 08</t>
+          <t>SACO OLIVEROS EL RETABLO</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-11.92078</t>
+          <t>-11.93601</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>-77.03832</t>
+          <t>-77.0582</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>572</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7073,32 +7073,32 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>303262</t>
+          <t>301531</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>MARCELINO CHAMPAGNAT</t>
+          <t>3082 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-11.90925</t>
+          <t>-11.965354</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>-77.04307</t>
+          <t>-77.059168</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>813</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7135,32 +7135,32 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>303399</t>
+          <t>301927</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>IVAN PAVLOV</t>
+          <t>COMERCIO 62 ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-11.92437</t>
+          <t>-11.93902</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>-77.04364</t>
+          <t>-77.05314</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>681</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7197,32 +7197,32 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>303417</t>
+          <t>301791</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>JESUS EL MAESTRO</t>
+          <t>CORONEL JOSE GALVEZ</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-11.91621</t>
+          <t>-11.91142</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>-77.03138</t>
+          <t>-77.01487</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>494</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7259,32 +7259,32 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>303549</t>
+          <t>301847</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>GENES DE PRIMAVERA</t>
+          <t>EL AMAUTA</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-11.92765</t>
+          <t>-11.92998</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>-77.054</t>
+          <t>-77.06647</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>835</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7321,32 +7321,32 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>303554</t>
+          <t>301885</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 11</t>
+          <t>LA ALBORADA FRANCESA</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-11.91561</t>
+          <t>-11.9123</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>-77.02516</t>
+          <t>-77.04734</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>673</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7383,32 +7383,32 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>303568</t>
+          <t>301456</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 13</t>
+          <t>3062 SANTA ROSA</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-11.9128</t>
+          <t>-11.94918</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>-77.0094</t>
+          <t>-77.0486</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1745</t>
+          <t>792</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7445,32 +7445,32 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>303667</t>
+          <t>301890</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>HUSARES DE JUNIN</t>
+          <t>PERUANO SUIZO</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-11.91534</t>
+          <t>-11.96703</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>-77.01432</t>
+          <t>-77.06011</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>785</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7507,32 +7507,32 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>303733</t>
+          <t>301395</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>PRESENTACION DE MARIA 41</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-11.95058</t>
+          <t>-11.91124</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>-77.05162</t>
+          <t>-77.01776</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -7569,42 +7569,42 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>303747</t>
+          <t>301475</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>JESUS OBRERO</t>
+          <t>8160 LOS CHASQUIS</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-11.95287</t>
+          <t>-11.93434</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>-77.05254</t>
+          <t>-77.06114</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>907</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7631,32 +7631,32 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>303752</t>
+          <t>301767</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 10</t>
+          <t>3066 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-11.91727</t>
+          <t>-11.94171</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>-77.0406</t>
+          <t>-77.04826</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>880</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7693,37 +7693,37 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>303771</t>
+          <t>618177</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>JESUS</t>
+          <t>MOM'S SCHOOL KINDERGARDEN</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-11.91625</t>
+          <t>-11.936886</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>-77.02771</t>
+          <t>-77.047864</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7755,37 +7755,37 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>303894</t>
+          <t>862683</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SARITA COLONIA</t>
+          <t>IVAN PAVLOV</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-11.92516</t>
+          <t>-11.921756</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>-77.04167</t>
+          <t>-77.043063</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>67</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7817,32 +7817,32 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>304148</t>
+          <t>301668</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>JAIME WHITE</t>
+          <t>2075 CRISTO HIJO DE DIOS</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-11.936118</t>
+          <t>-11.92201</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>-77.044542</t>
+          <t>-77.02409</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>694</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7879,32 +7879,32 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>304266</t>
+          <t>301786</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>LICEO SANTO DOMINGO</t>
+          <t>3096 FRANZ TAMAYO SOLARES</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-11.91322</t>
+          <t>-11.92383</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>-77.05263</t>
+          <t>-77.05296</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>926</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7941,42 +7941,42 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>304290</t>
+          <t>301418</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SONIA AMADOR JAIME</t>
+          <t>2077 SAN MARTIN DE PORRES DE AÑO NUEVO / SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-11.95381</t>
+          <t>-11.92842</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>-77.05101</t>
+          <t>-77.04119</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>942</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8003,32 +8003,32 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>304501</t>
+          <t>301753</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>JACK GOLDFARB</t>
+          <t>3065 VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-11.94846</t>
+          <t>-11.93866</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>-77.05007</t>
+          <t>-77.04106</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>887</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8065,32 +8065,32 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>333184</t>
+          <t>301833</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2079 ANTONIO RAIMONDI</t>
+          <t>RAMON CASTILLA</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-11.95251</t>
+          <t>-11.93282</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>-77.06737</t>
+          <t>-77.05559</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>760</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8127,32 +8127,32 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>333278</t>
+          <t>302903</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>3024 JOSE ANTONIO ENCINAS</t>
+          <t>LA FE DE MARIA</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-11.94278</t>
+          <t>-11.93455</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>-77.06833</t>
+          <t>-77.04457</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>611</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8189,32 +8189,32 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>336427</t>
+          <t>333184</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>UNION LOS OLIVOS</t>
+          <t>2079 ANTONIO RAIMONDI</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-11.9476</t>
+          <t>-11.95251</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>-77.067533</t>
+          <t>-77.06737</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>926</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -8251,37 +8251,37 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>398095</t>
+          <t>303064</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>MI PEQUEÑO MUNDO DE SANTA LUZMILA</t>
+          <t>FE Y ALEGRIA 08</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>-11.94454</t>
+          <t>-11.92078</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>-77.06369</t>
+          <t>-77.03832</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8313,32 +8313,32 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>506194</t>
+          <t>301729</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>8181 HEROES DEL ALTO CENEPA</t>
+          <t>3076 SANTA ROSA</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>-11.92344</t>
+          <t>-11.91084</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>-77.06047</t>
+          <t>-77.00576</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8375,32 +8375,32 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>514740</t>
+          <t>302922</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>BARTON DE COMAS</t>
+          <t>JOHANNES GUTENBERG</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>-11.96869</t>
+          <t>-11.90077</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>-77.06034</t>
+          <t>-77.04648</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>786</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -8437,32 +8437,32 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>526917</t>
+          <t>303747</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>JESUS, NUESTRO AMIGO DE LA LIBERTAD</t>
+          <t>JESUS OBRERO</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>-11.95754</t>
+          <t>-11.95287</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>-77.04913</t>
+          <t>-77.05254</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>624</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -8499,32 +8499,32 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>534390</t>
+          <t>709894</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE MONSERRAT DE COMAS</t>
+          <t>SANTA MARIA LA REINA</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>-11.96929</t>
+          <t>-11.914505</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>-77.06027</t>
+          <t>-77.035188</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>277</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -8561,37 +8561,37 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>549264</t>
+          <t>711482</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>SONIA AMADOR JAIME II</t>
+          <t>DELTA</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>-11.95313</t>
+          <t>-11.9053</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>-77.05053</t>
+          <t>-77.04044</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>564424</t>
+          <t>301705</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>GETSEMANI</t>
+          <t>2026 SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>-11.91227</t>
+          <t>-11.95063</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>-77.02747</t>
+          <t>-77.06313</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>942</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8685,32 +8685,32 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>582461</t>
+          <t>333278</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CRISTO RAMOS</t>
+          <t>3024 JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>-11.95741</t>
+          <t>-11.94278</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>-77.04122</t>
+          <t>-77.06833</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>998</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8747,32 +8747,32 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>597113</t>
+          <t>301692</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>TRENTO PRO</t>
+          <t>LIBERTAD</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>-11.9276</t>
+          <t>-11.9224</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>-77.07216</t>
+          <t>-77.03899</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8809,37 +8809,37 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>605245</t>
+          <t>301814</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>BERNE</t>
+          <t>2031 JOSE VALVERDE CARO</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>-11.95314</t>
+          <t>-11.94512</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>-77.0529</t>
+          <t>-77.03126</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8871,37 +8871,37 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>618177</t>
+          <t>303752</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>MOM'S SCHOOL KINDERGARDEN</t>
+          <t>FE Y ALEGRIA 10</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>-11.936886</t>
+          <t>-11.91727</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>-77.047864</t>
+          <t>-77.0406</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>986</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8933,32 +8933,32 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>625309</t>
+          <t>801524</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>SANTA BEATRIZ</t>
+          <t>TECHNOLOGY SCHOOLS DEL RETABLO I</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>-11.9466</t>
+          <t>-11.93572</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>-77.0681</t>
+          <t>-77.05902</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8995,32 +8995,32 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>655155</t>
+          <t>303554</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>HOWARD GARDNER DE LIMA NORTE</t>
+          <t>FE Y ALEGRIA 11</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>-11.95384</t>
+          <t>-11.91561</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>-77.05766</t>
+          <t>-77.02516</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -9057,32 +9057,32 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>708880</t>
+          <t>301871</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE GUADALUPE SEGUNDO</t>
+          <t>MARISCAL ANDRES AVELINO CACERES DORREGARAY</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>-11.95863</t>
+          <t>-11.91639</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>-77.0525</t>
+          <t>-77.03376</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>700</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9119,32 +9119,32 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>709894</t>
+          <t>301913</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>SANTA MARIA LA REINA</t>
+          <t>SAN FELIPE</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>-11.914505</t>
+          <t>-11.89896</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>-77.035188</t>
+          <t>-77.04063</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9181,32 +9181,32 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>710232</t>
+          <t>303568</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>CANTOR COLLEGE</t>
+          <t>FE Y ALEGRIA 13</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>-11.96568</t>
+          <t>-11.9128</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>-77.06135</t>
+          <t>-77.0094</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -9243,32 +9243,32 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>710562</t>
+          <t>301748</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>GENES EL PINAR - COMAS</t>
+          <t>3047 REPUBLICA DE CANADA</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>-11.9158</t>
+          <t>-11.95916</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>-77.04904</t>
+          <t>-77.04107</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>933</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -9305,37 +9305,37 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>710944</t>
+          <t>303733</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>TRILCE DE COMAS</t>
+          <t>PRESENTACION DE MARIA 41</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>-11.95351</t>
+          <t>-11.95058</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>-77.05374</t>
+          <t>-77.05162</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>971</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>67</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -9367,37 +9367,37 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>711019</t>
+          <t>549264</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>JESUS ANGELES</t>
+          <t>SONIA AMADOR JAIME II</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>-11.94049</t>
+          <t>-11.95313</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>-77.06656</t>
+          <t>-77.05053</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9429,37 +9429,37 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>711482</t>
+          <t>301687</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>DELTA</t>
+          <t>PERU-HOLANDA</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>-11.9053</t>
+          <t>-11.91663</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>-77.04044</t>
+          <t>-77.03561</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>73</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9491,32 +9491,32 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>711712</t>
+          <t>301625</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>MARIA DEL ANGEL</t>
+          <t>2048 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>-11.95204</t>
+          <t>-11.939926</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>-77.05456</t>
+          <t>-77.063361</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -9553,32 +9553,32 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>711854</t>
+          <t>301772</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>BILINGUE FEDERICO VILLARREAL / FEDERICO VILLARREAL - BILINGÜE</t>
+          <t>2085 SAN AGUSTIN</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>-11.95837</t>
+          <t>-11.9323</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>-77.05256</t>
+          <t>-77.05056</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9615,32 +9615,32 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>712387</t>
+          <t>303894</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>TRILCE LAS VEGAS</t>
+          <t>SARITA COLONIA</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>-11.95344</t>
+          <t>-11.92516</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>-77.05957</t>
+          <t>-77.04167</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>277</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -9677,37 +9677,37 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>744878</t>
+          <t>304290</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>ALFA COMAS</t>
+          <t>SONIA AMADOR JAIME</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>-11.94338</t>
+          <t>-11.95381</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>-77.06514</t>
+          <t>-77.05101</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -9739,32 +9739,32 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>745552</t>
+          <t>301611</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>AL GORE</t>
+          <t>2022 SINCHI ROCA</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>-11.948187</t>
+          <t>-11.93045</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>-77.050972</t>
+          <t>-77.04964</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9801,32 +9801,32 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>801524</t>
+          <t>301630</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>TECHNOLOGY SCHOOLS DEL RETABLO I</t>
+          <t>3055 TUPAC AMARU</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>-11.93572</t>
+          <t>-11.93503</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>-77.05902</t>
+          <t>-77.04317</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>87</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9863,32 +9863,32 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>812037</t>
+          <t>301178</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL ASTURIAS DE CARABAYLLO</t>
+          <t>02 JOSE GALVITO</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>-11.91529</t>
+          <t>-11.911038</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>-77.0266</t>
+          <t>-77.012883</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>208</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9925,37 +9925,37 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>823168</t>
+          <t>304148</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>SANTO TOMAS</t>
+          <t>JAIME WHITE</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>-11.92611</t>
+          <t>-11.936118</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>-77.04322</t>
+          <t>-77.044542</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>333</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -9987,37 +9987,37 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>826807</t>
+          <t>398095</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS EL RETABLO</t>
+          <t>MI PEQUEÑO MUNDO DE SANTA LUZMILA</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>-11.93601</t>
+          <t>-11.94454</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>-77.0582</t>
+          <t>-77.06369</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>142</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -10049,37 +10049,37 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>851458</t>
+          <t>526917</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>MARIA MONTESSORI STOPPIANI / NUEVO MONTESSORI II</t>
+          <t>JESUS, NUESTRO AMIGO DE LA LIBERTAD</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>-11.911136</t>
+          <t>-11.95754</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>-77.022336</t>
+          <t>-77.04913</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>83</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -10111,37 +10111,37 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>862169</t>
+          <t>301932</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>MARIA MEDALLA MILAGROSA</t>
+          <t>CARLOS WIESSE</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>-11.906485</t>
+          <t>-11.9519</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>-77.05296</t>
+          <t>-77.0505</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -10173,42 +10173,42 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>862683</t>
+          <t>301649</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>IVAN PAVLOV</t>
+          <t>ESTADOS UNIDOS</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>-11.921756</t>
+          <t>-11.965191</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>-77.043063</t>
+          <t>-77.05676</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -10235,32 +10235,32 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>903419</t>
+          <t>304266</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>PROLOG DE COMAS</t>
+          <t>LICEO SANTO DOMINGO</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>-11.94369</t>
+          <t>-11.91322</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>-77.05001</t>
+          <t>-77.05263</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-COMAS.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-COMAS.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>301003</t>
+          <t>903419</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>354 NUESTRA SEÑORA DE FATIMA</t>
+          <t>PROLOG DE COMAS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-11.92742</t>
+          <t>219</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.056</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>-11.94369</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.05001</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>301022</t>
+          <t>862683</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>IVAN PAVLOV</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.93322</t>
+          <t>67</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.05404</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>-11.921756</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.043063</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>301036</t>
+          <t>862169</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>370 VIRGEN DE LA PUERTA</t>
+          <t>MARIA MEDALLA MILAGROSA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.95692</t>
+          <t>430</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.03582</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>-11.906485</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.05296</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>301041</t>
+          <t>851458</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>MARIA MONTESSORI STOPPIANI / NUEVO MONTESSORI II</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-11.95157</t>
+          <t>545</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.0574</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>-11.911136</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.022336</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>302762</t>
+          <t>826807</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SANTO TOMAS</t>
+          <t>SACO OLIVEROS EL RETABLO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.92786</t>
+          <t>572</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.04616</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>-11.93601</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.0582</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>605245</t>
+          <t>823168</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BERNE</t>
+          <t>SANTO TOMAS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.95314</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.0529</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>-11.92611</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.04322</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>710944</t>
+          <t>812037</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TRILCE DE COMAS</t>
+          <t>MIGUEL ANGEL ASTURIAS DE CARABAYLLO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.95351</t>
+          <t>460</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.05374</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>-11.91529</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.0266</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>823168</t>
+          <t>801524</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SANTO TOMAS</t>
+          <t>TECHNOLOGY SCHOOLS DEL RETABLO I</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.92611</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.04322</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>-11.93572</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.05902</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14945</t>
+          <t>745552</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ANGELITOS DE SANTA MARIA</t>
+          <t>AL GORE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-11.91243</t>
+          <t>341</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.02597</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>-11.948187</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.050972</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>300918</t>
+          <t>744878</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>ALFA COMAS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-11.9662</t>
+          <t>234</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.05441</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>-11.94338</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.06514</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>300937</t>
+          <t>712387</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>TRILCE LAS VEGAS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.92047</t>
+          <t>271</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.04411</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>-11.95344</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.05957</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>300980</t>
+          <t>711854</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>341 EL RETABLO</t>
+          <t>BILINGUE FEDERICO VILLARREAL / FEDERICO VILLARREAL - BILINGÜE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.93803</t>
+          <t>234</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.05577</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>-11.95837</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.05256</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>301017</t>
+          <t>711712</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>356 ANGELITOS DEL ALAMO</t>
+          <t>MARIA DEL ANGEL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-11.93107</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.06794</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>-11.95204</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.05456</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,37 +1307,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>301102</t>
+          <t>711482</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>DELTA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-11.9098</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.04598</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>-11.9053</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.04044</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1369,37 +1369,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>301197</t>
+          <t>711019</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>JESUS ANGELES</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-11.959535</t>
+          <t>56</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.04419</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>-11.94049</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.06656</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>301201</t>
+          <t>710944</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>316 SAN FELIPE</t>
+          <t>TRILCE DE COMAS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-11.90046</t>
+          <t>797</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.04003</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>-11.95351</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.05374</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>302026</t>
+          <t>710562</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>GENES EL PINAR - COMAS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.92054</t>
+          <t>203</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.03962</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>-11.9158</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.04904</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>303549</t>
+          <t>710232</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GENES DE PRIMAVERA</t>
+          <t>CANTOR COLLEGE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-11.92765</t>
+          <t>318</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.054</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>-11.96568</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.06135</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>625309</t>
+          <t>709894</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SANTA BEATRIZ</t>
+          <t>SANTA MARIA LA REINA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-11.9466</t>
+          <t>277</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.0681</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>-11.914505</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.035188</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>564424</t>
+          <t>708880</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GETSEMANI</t>
+          <t>NUESTRA SEÑORA DE GUADALUPE SEGUNDO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-11.91227</t>
+          <t>277</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.02747</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>-11.95863</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.0525</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>712387</t>
+          <t>655155</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TRILCE LAS VEGAS</t>
+          <t>HOWARD GARDNER DE LIMA NORTE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-11.95344</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.05957</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>-11.95384</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.05766</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>300956</t>
+          <t>625309</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>326 MARIA MONTESSORI</t>
+          <t>SANTA BEATRIZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-11.95697</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.05621</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>-11.9466</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.0681</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,37 +1865,37 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>301215</t>
+          <t>618177</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>MOM'S SCHOOL KINDERGARDEN</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-11.90765</t>
+          <t>44</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.03788</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>-11.936886</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.047864</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1927,37 +1927,37 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>514740</t>
+          <t>605245</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BARTON DE COMAS</t>
+          <t>BERNE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-11.96869</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.06034</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>-11.95314</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.0529</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>300975</t>
+          <t>597113</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>337 SANGARARA</t>
+          <t>TRENTO PRO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-11.92474</t>
+          <t>316</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.04515</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>-11.9276</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.07216</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>301116</t>
+          <t>582461</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CARMEN ALTO</t>
+          <t>CRISTO RAMOS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-11.94631</t>
+          <t>334</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.03114</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>-11.95741</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.04122</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>301319</t>
+          <t>564424</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2035 FERNANDO BELAUNDE TERRY</t>
+          <t>GETSEMANI</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-11.94199</t>
+          <t>228</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.03513</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>-11.91227</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.02747</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,37 +2175,37 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>301480</t>
+          <t>549264</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>SONIA AMADOR JAIME II</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-11.96378</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.06124</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>-11.95313</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.05053</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>301574</t>
+          <t>534390</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>8156 PERUANO ALEMAN</t>
+          <t>NUESTRA SEÑORA DE MONSERRAT DE COMAS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-11.90871</t>
+          <t>339</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.04278</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>-11.96929</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.06027</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2299,37 +2299,37 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>303771</t>
+          <t>526917</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>JESUS</t>
+          <t>JESUS, NUESTRO AMIGO DE LA LIBERTAD</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-11.91625</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.02771</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>-11.95754</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.04913</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>710562</t>
+          <t>514740</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GENES EL PINAR - COMAS</t>
+          <t>BARTON DE COMAS</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-11.9158</t>
+          <t>311</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.04904</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>-11.96869</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.06034</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>812037</t>
+          <t>506194</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL ASTURIAS DE CARABAYLLO</t>
+          <t>8181 HEROES DEL ALTO CENEPA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-11.91529</t>
+          <t>744</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-77.0266</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>-11.92344</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.06047</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2485,37 +2485,37 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>851458</t>
+          <t>398095</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MARIA MONTESSORI STOPPIANI / NUEVO MONTESSORI II</t>
+          <t>MI PEQUEÑO MUNDO DE SANTA LUZMILA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-11.911136</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.022336</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>-11.94454</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.06369</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>300881</t>
+          <t>336427</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SANGARARA</t>
+          <t>UNION LOS OLIVOS</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-11.915543</t>
+          <t>304</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.055633</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>-11.9476</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.067533</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>300961</t>
+          <t>333278</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>3024 JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-11.94098</t>
+          <t>998</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.06309</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>-11.94278</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.06833</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>301164</t>
+          <t>333184</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>368 ANGELITOS DE JESUS</t>
+          <t>2079 ANTONIO RAIMONDI</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-11.91963</t>
+          <t>926</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.05964</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>-11.95251</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.06737</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>301404</t>
+          <t>304501</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2072 LEV SEMIONOVICH VIGOTSKI</t>
+          <t>JACK GOLDFARB</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-11.90473</t>
+          <t>288</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-77.05477</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>-11.94846</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.05007</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2795,42 +2795,42 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>301550</t>
+          <t>304290</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>3085 PEDRO VILCA APAZA</t>
+          <t>SONIA AMADOR JAIME</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-11.95164</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-77.05717</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>-11.95381</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.05101</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>302229</t>
+          <t>304266</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>LA SEMILLITA</t>
+          <t>LICEO SANTO DOMINGO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-11.95989</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-77.04742</t>
+          <t>92</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>-11.91322</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.05263</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>302253</t>
+          <t>304148</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PAUL GROUSSAC DE HUAQUILLAY</t>
+          <t>JAIME WHITE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-11.946962</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-77.050972</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>-11.936118</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.044542</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>708880</t>
+          <t>303894</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE GUADALUPE SEGUNDO</t>
+          <t>SARITA COLONIA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-11.95863</t>
+          <t>277</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-77.0525</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>-11.92516</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.04167</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>301135</t>
+          <t>303771</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>LUIS ENRIQUE II</t>
+          <t>JESUS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-11.91925</t>
+          <t>234</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-77.03833</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>-11.91625</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.02771</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>302012</t>
+          <t>303752</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>LUIS ENRIQUE XVII</t>
+          <t>FE Y ALEGRIA 10</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-11.93585</t>
+          <t>986</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-77.05155</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>-11.91727</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.0406</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,37 +3167,37 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>303262</t>
+          <t>303747</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MARCELINO CHAMPAGNAT</t>
+          <t>JESUS OBRERO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-11.90925</t>
+          <t>624</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-77.04307</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>-11.95287</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.05254</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>582461</t>
+          <t>303733</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CRISTO RAMOS</t>
+          <t>PRESENTACION DE MARIA 41</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-11.95741</t>
+          <t>971</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-77.04122</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>-11.95058</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.05162</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>711854</t>
+          <t>303667</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>BILINGUE FEDERICO VILLARREAL / FEDERICO VILLARREAL - BILINGÜE</t>
+          <t>HUSARES DE JUNIN</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-11.95837</t>
+          <t>314</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-77.05256</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>-11.91534</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.01432</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>300895</t>
+          <t>303568</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>LUIS ENRIQUE XIV</t>
+          <t>FE Y ALEGRIA 13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-11.9141</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-77.0112</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>-11.9128</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.0094</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>301121</t>
+          <t>303554</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>888 SEÑOR DE LOS MILAGROS</t>
+          <t>FE Y ALEGRIA 11</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-11.91563</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-77.03456</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>-11.91561</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.02516</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>301140</t>
+          <t>303549</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>LUIS ENRIQUE XIII</t>
+          <t>GENES DE PRIMAVERA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-11.90842</t>
+          <t>235</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-77.04148</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>-11.92765</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.054</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>301159</t>
+          <t>303417</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>JESUS EL MAESTRO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-11.94334</t>
+          <t>260</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-77.05569</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>-11.91621</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.03138</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>301965</t>
+          <t>303399</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SANTA LUZMILA</t>
+          <t>IVAN PAVLOV</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-11.945741</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-77.059053</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>-11.92437</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.04364</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>303399</t>
+          <t>303262</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>IVAN PAVLOV</t>
+          <t>MARCELINO CHAMPAGNAT</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-11.92437</t>
+          <t>237</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-77.04364</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>-11.90925</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.04307</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>336427</t>
+          <t>303064</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>UNION LOS OLIVOS</t>
+          <t>FE Y ALEGRIA 08</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-11.9476</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-77.067533</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>-11.92078</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.03832</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>230713</t>
+          <t>302998</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MARIO VARGAS LLOSA</t>
+          <t>CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-11.92458</t>
+          <t>327</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-77.05362</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>-11.94305</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.04706</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>301183</t>
+          <t>302922</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>JOHANNES GUTENBERG</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-11.9381</t>
+          <t>786</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-77.04256</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>-11.90077</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.04648</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,37 +3911,37 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>302309</t>
+          <t>302917</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE GUADALUPE</t>
+          <t>INGENIERIA DE LA ENSEÑANZA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-11.96009</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-77.05316</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>-11.95284</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.05339</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>303417</t>
+          <t>302903</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>JESUS EL MAESTRO</t>
+          <t>LA FE DE MARIA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-11.91621</t>
+          <t>611</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-77.03138</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>-11.93455</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.04457</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>534390</t>
+          <t>302842</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE MONSERRAT DE COMAS</t>
+          <t>SAN VICENTE</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-11.96929</t>
+          <t>912</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-77.06027</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>-11.93511</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.05883</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>711712</t>
+          <t>302818</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MARIA DEL ANGEL</t>
+          <t>SOR ANA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-11.95204</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-77.05456</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>-11.9191</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.04215</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>301357</t>
+          <t>302762</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2046 VIRGEN DE LAS MERCEDES</t>
+          <t>SANTO TOMAS</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-11.97198</t>
+          <t>216</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-77.05695</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>-11.92786</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.04616</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>301606</t>
+          <t>302724</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>8173 SANTA ISOLINA</t>
+          <t>ANTON MAKARENKO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-11.95911</t>
+          <t>387</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-77.06226</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>-11.91467</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.04298</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>301908</t>
+          <t>302333</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SAN CARLOS</t>
+          <t>MATEMATICO HONORES DEL PINAR</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-11.90316</t>
+          <t>306</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-77.04262</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>-11.92093</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.05871</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>597113</t>
+          <t>302309</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>TRENTO PRO</t>
+          <t>NUESTRA SEÑORA DE GUADALUPE</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-11.9276</t>
+          <t>416</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-77.07216</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>-11.96009</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.05316</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>655155</t>
+          <t>302253</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>HOWARD GARDNER DE LIMA NORTE</t>
+          <t>PAUL GROUSSAC DE HUAQUILLAY</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-11.95384</t>
+          <t>277</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-77.05766</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>-11.946962</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.050972</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,37 +4469,37 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>302111</t>
+          <t>302229</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>ESPIRITU SANTO</t>
+          <t>LA SEMILLITA</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-11.93762</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-77.05025</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-11.95989</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-77.04742</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4531,37 +4531,37 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>302818</t>
+          <t>302111</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SOR ANA DE LOS ANGELES</t>
+          <t>ESPIRITU SANTO</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-11.9191</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-77.04215</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>-11.93762</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.05025</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4593,37 +4593,37 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>302917</t>
+          <t>302050</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>INGENIERIA DE LA ENSEÑANZA</t>
+          <t>8186 MARIA JESUS ESPINOZA MATOS</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-11.95284</t>
+          <t>550</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-77.05339</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>-11.89907</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.04858</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>302998</t>
+          <t>302026</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO</t>
+          <t>01</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-11.94305</t>
+          <t>274</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-77.04706</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>-11.92054</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.03962</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>301526</t>
+          <t>302012</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>3077 EL ALAMO</t>
+          <t>LUIS ENRIQUE XVII</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-11.93319</t>
+          <t>381</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-77.06758</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>-11.93585</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.05155</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4779,42 +4779,42 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>301588</t>
+          <t>301970</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>8157 REPUBLICA DE FRANCIA</t>
+          <t>3068 SAN JUDAS TADEO</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-11.91219</t>
+          <t>473</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-77.04131</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>-11.95762</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.05009</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>744878</t>
+          <t>301965</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ALFA COMAS</t>
+          <t>SANTA LUZMILA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-11.94338</t>
+          <t>365</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-77.06514</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>-11.945741</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.059053</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,42 +4903,42 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>300876</t>
+          <t>301932</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>LA PASCANA</t>
+          <t>CARLOS WIESSE</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-11.93643</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-77.04637</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>-11.9519</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.0505</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>301324</t>
+          <t>301927</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2042 FRAY MARTIN DE PORRES</t>
+          <t>COMERCIO 62 ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-11.96187</t>
+          <t>681</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-77.04706</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>-11.93902</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.05314</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>301512</t>
+          <t>301913</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>3072 AUGUSTO SALAZAR BONDY</t>
+          <t>SAN FELIPE</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-11.94652</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-77.06183</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>-11.89896</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.04063</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>301258</t>
+          <t>301908</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>SAN CARLOS</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-11.93058</t>
+          <t>375</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-77.05648</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>-11.90316</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.04262</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>301277</t>
+          <t>301890</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2016 FRANCISCO BOLOGNESI</t>
+          <t>PERUANO SUIZO</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-11.94477</t>
+          <t>785</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-77.05477</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>-11.96703</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.06011</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>301442</t>
+          <t>301885</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>3060 ALFONSO UGARTE VERNAL</t>
+          <t>LA ALBORADA FRANCESA</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-11.93905</t>
+          <t>673</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-77.05315</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>-11.9123</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.04734</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5275,42 +5275,42 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>301970</t>
+          <t>301871</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>3068 SAN JUDAS TADEO</t>
+          <t>MARISCAL ANDRES AVELINO CACERES DORREGARAY</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-11.95762</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-77.05009</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>-11.91639</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.03376</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>303667</t>
+          <t>301866</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>HUSARES DE JUNIN</t>
+          <t>JUAN PABLO VIZCARDO Y GUZMAN</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-11.91534</t>
+          <t>354</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-77.01432</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>-11.92554</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.04526</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>301593</t>
+          <t>301847</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>8158 ISABEL FLORES DE OLIVA</t>
+          <t>EL AMAUTA</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-11.91616</t>
+          <t>835</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-77.050005</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>-11.92998</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.06647</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>301734</t>
+          <t>301833</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>8170 CESAR VALLEJO</t>
+          <t>RAMON CASTILLA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-11.93162</t>
+          <t>760</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-77.03668</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>-11.93282</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.05559</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>302842</t>
+          <t>301828</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SAN VICENTE</t>
+          <t>JOSE MARTI</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-11.93511</t>
+          <t>711</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-77.05883</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>-11.95403</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.05587</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>710232</t>
+          <t>301814</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CANTOR COLLEGE</t>
+          <t>2031 JOSE VALVERDE CARO</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-11.96568</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-77.06135</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>-11.94512</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.03126</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>301300</t>
+          <t>301809</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2033 NUESTRA SEÑORA DE FATIMA</t>
+          <t>2038 INCA GARCILASO DE LA VEGA</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-11.95544</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-77.05324</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>-11.917908</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-77.029028</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>301338</t>
+          <t>301791</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2043 SANGARARA</t>
+          <t>CORONEL JOSE GALVEZ</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-11.91968</t>
+          <t>494</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-77.0442</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>-11.91142</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-77.01487</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>302050</t>
+          <t>301786</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>8186 MARIA JESUS ESPINOZA MATOS</t>
+          <t>3096 FRANZ TAMAYO SOLARES</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-11.89907</t>
+          <t>926</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-77.04858</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>-11.92383</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-77.05296</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>301282</t>
+          <t>301772</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2020 MAESTRO JOSE ANTONIO ENCINAS</t>
+          <t>2085 SAN AGUSTIN</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-11.93864</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-77.05562</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>-11.9323</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-77.05056</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>301866</t>
+          <t>301767</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>JUAN PABLO VIZCARDO Y GUZMAN</t>
+          <t>3066 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-11.92554</t>
+          <t>880</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-77.04526</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>-11.94171</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-77.04826</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>302333</t>
+          <t>301753</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MATEMATICO HONORES DEL PINAR</t>
+          <t>3065 VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-11.92093</t>
+          <t>887</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-77.05871</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>-11.93866</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-77.04106</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6019,32 +6019,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>302724</t>
+          <t>301748</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ANTON MAKARENKO</t>
+          <t>3047 REPUBLICA DE CANADA</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-11.91467</t>
+          <t>933</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-77.04298</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>-11.95916</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-77.04107</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6081,32 +6081,32 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>745552</t>
+          <t>301734</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>AL GORE</t>
+          <t>8170 CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-11.948187</t>
+          <t>419</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-77.050972</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>-11.93162</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-77.03668</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6143,32 +6143,32 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>301423</t>
+          <t>301729</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>3076 SANTA ROSA</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-11.90724</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-77.03831</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>-11.91084</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-77.00576</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6205,32 +6205,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>301437</t>
+          <t>301710</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2100 JUAN VELASCO ALVARADO</t>
+          <t>3061 JORGE CHAVEZ DARTNELL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-11.95464</t>
+          <t>665</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-77.05504</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>-11.95925</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-77.0521</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>301461</t>
+          <t>301705</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>2026 SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-11.94199</t>
+          <t>942</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-77.04259</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>-11.95063</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-77.06313</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6329,37 +6329,37 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>711019</t>
+          <t>301692</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>JESUS ANGELES</t>
+          <t>LIBERTAD</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-11.94049</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-77.06656</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-11.9224</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-77.03899</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>301499</t>
+          <t>301687</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>PERU-HOLANDA</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-11.95767</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-77.04014</t>
+          <t>73</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>-11.91663</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-77.03561</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>304501</t>
+          <t>301668</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>JACK GOLDFARB</t>
+          <t>2075 CRISTO HIJO DE DIOS</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-11.94846</t>
+          <t>694</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-77.05007</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>-11.92201</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-77.02409</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6515,32 +6515,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>301381</t>
+          <t>301649</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2059 SUECIA</t>
+          <t>ESTADOS UNIDOS</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-11.92514</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-77.03878</t>
+          <t>91</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>-11.965191</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-77.05676</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6577,32 +6577,32 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>301710</t>
+          <t>301630</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>3061 JORGE CHAVEZ DARTNELL</t>
+          <t>3055 TUPAC AMARU</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-11.95925</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-77.0521</t>
+          <t>87</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>-11.93503</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-77.04317</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>301828</t>
+          <t>301625</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>JOSE MARTI</t>
+          <t>2048 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-11.95403</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-77.05587</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>-11.939926</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-77.063361</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6701,32 +6701,32 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>862169</t>
+          <t>301611</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>MARIA MEDALLA MILAGROSA</t>
+          <t>2022 SINCHI ROCA</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-11.906485</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-77.05296</t>
+          <t>84</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>-11.93045</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-77.04964</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6763,32 +6763,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>301376</t>
+          <t>301606</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2055 PRIMERO DE ABRIL</t>
+          <t>8173 SANTA ISOLINA</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-11.91554</t>
+          <t>446</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-77.04418</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>-11.95911</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-77.06226</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6825,32 +6825,32 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>301809</t>
+          <t>301593</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2038 INCA GARCILASO DE LA VEGA</t>
+          <t>8158 ISABEL FLORES DE OLIVA</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-11.917908</t>
+          <t>503</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-77.029028</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>-11.91616</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-77.050005</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6887,32 +6887,32 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>903419</t>
+          <t>301588</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>PROLOG DE COMAS</t>
+          <t>8157 REPUBLICA DE FRANCIA</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-11.94369</t>
+          <t>522</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>-77.05001</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>-11.91219</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-77.04131</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6949,32 +6949,32 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>506194</t>
+          <t>301574</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>8181 HEROES DEL ALTO CENEPA</t>
+          <t>8156 PERUANO ALEMAN</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-11.92344</t>
+          <t>309</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>-77.06047</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>-11.90871</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-77.04278</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -7011,32 +7011,32 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>826807</t>
+          <t>301550</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS EL RETABLO</t>
+          <t>3085 PEDRO VILCA APAZA</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-11.93601</t>
+          <t>389</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>-77.0582</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>-11.95164</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-77.05717</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
           <t>-11.965354</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="J108" t="inlineStr">
         <is>
           <t>-77.059168</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -7135,32 +7135,32 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>301927</t>
+          <t>301526</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>COMERCIO 62 ALMIRANTE MIGUEL GRAU</t>
+          <t>3077 EL ALAMO</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-11.93902</t>
+          <t>508</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>-77.05314</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>-11.93319</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-77.06758</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7197,32 +7197,32 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>301791</t>
+          <t>301512</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CORONEL JOSE GALVEZ</t>
+          <t>3072 AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-11.91142</t>
+          <t>732</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>-77.01487</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>-11.94652</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-77.06183</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7259,32 +7259,32 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>301847</t>
+          <t>301499</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>EL AMAUTA</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-11.92998</t>
+          <t>571</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>-77.06647</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>-11.95767</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-77.04014</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7321,32 +7321,32 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>301885</t>
+          <t>301480</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>LA ALBORADA FRANCESA</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-11.9123</t>
+          <t>340</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>-77.04734</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>-11.96378</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-77.06124</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7383,32 +7383,32 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>301456</t>
+          <t>301475</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>3062 SANTA ROSA</t>
+          <t>8160 LOS CHASQUIS</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-11.94918</t>
+          <t>907</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>-77.0486</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>-11.93434</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-77.06114</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7445,32 +7445,32 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>301890</t>
+          <t>301461</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>PERUANO SUIZO</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-11.96703</t>
+          <t>709</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>-77.06011</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>-11.94199</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-77.04259</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7507,32 +7507,32 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>301395</t>
+          <t>301456</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>3062 SANTA ROSA</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-11.91124</t>
+          <t>792</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>-77.01776</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>-11.94918</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-77.0486</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -7569,32 +7569,32 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>301475</t>
+          <t>301442</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>8160 LOS CHASQUIS</t>
+          <t>3060 ALFONSO UGARTE VERNAL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-11.93434</t>
+          <t>557</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>-77.06114</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>-11.93905</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-77.05315</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7631,32 +7631,32 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>301767</t>
+          <t>301437</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>3066 SEÑOR DE LOS MILAGROS</t>
+          <t>2100 JUAN VELASCO ALVARADO</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-11.94171</t>
+          <t>661</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>-77.04826</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>-11.95464</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-77.05504</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7693,37 +7693,37 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>618177</t>
+          <t>301423</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>MOM'S SCHOOL KINDERGARDEN</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-11.936886</t>
+          <t>681</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>-77.047864</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-11.90724</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-77.03831</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7755,42 +7755,42 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>862683</t>
+          <t>301418</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>IVAN PAVLOV</t>
+          <t>2077 SAN MARTIN DE PORRES DE AÑO NUEVO / SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-11.921756</t>
+          <t>942</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>-77.043063</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>-11.92842</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-77.04119</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7817,32 +7817,32 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>301668</t>
+          <t>301404</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2075 CRISTO HIJO DE DIOS</t>
+          <t>2072 LEV SEMIONOVICH VIGOTSKI</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-11.92201</t>
+          <t>354</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>-77.02409</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>-11.90473</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-77.05477</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7879,32 +7879,32 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>301786</t>
+          <t>301395</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>3096 FRANZ TAMAYO SOLARES</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-11.92383</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>-77.05296</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>-11.91124</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-77.01776</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7941,32 +7941,32 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>301418</t>
+          <t>301381</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2077 SAN MARTIN DE PORRES DE AÑO NUEVO / SAN MARTIN DE PORRES</t>
+          <t>2059 SUECIA</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-11.92842</t>
+          <t>659</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>-77.04119</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>-11.92514</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-77.03878</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8003,32 +8003,32 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>301753</t>
+          <t>301376</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>3065 VIRGEN DEL CARMEN</t>
+          <t>2055 PRIMERO DE ABRIL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-11.93866</t>
+          <t>670</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>-77.04106</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>-11.91554</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-77.04418</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8065,32 +8065,32 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>301833</t>
+          <t>301357</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>RAMON CASTILLA</t>
+          <t>2046 VIRGEN DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-11.93282</t>
+          <t>432</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>-77.05559</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>-11.97198</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-77.05695</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8127,32 +8127,32 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>302903</t>
+          <t>301338</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>LA FE DE MARIA</t>
+          <t>2043 SANGARARA</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-11.93455</t>
+          <t>570</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>-77.04457</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>-11.91968</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-77.0442</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8189,32 +8189,32 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>333184</t>
+          <t>301324</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2079 ANTONIO RAIMONDI</t>
+          <t>2042 FRAY MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-11.95251</t>
+          <t>511</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>-77.06737</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>-11.96187</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-77.04706</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -8251,32 +8251,32 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>303064</t>
+          <t>301319</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 08</t>
+          <t>2035 FERNANDO BELAUNDE TERRY</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>-11.92078</t>
+          <t>368</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>-77.03832</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>-11.94199</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-77.03513</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8313,32 +8313,32 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>301729</t>
+          <t>301300</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>3076 SANTA ROSA</t>
+          <t>2033 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>-11.91084</t>
+          <t>604</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>-77.00576</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>-11.95544</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-77.05324</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8375,32 +8375,32 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>302922</t>
+          <t>301282</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>JOHANNES GUTENBERG</t>
+          <t>2020 MAESTRO JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>-11.90077</t>
+          <t>639</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>-77.04648</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>-11.93864</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-77.05562</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -8437,37 +8437,37 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>303747</t>
+          <t>301277</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>JESUS OBRERO</t>
+          <t>2016 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>-11.95287</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>-77.05254</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>-11.94477</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-77.05477</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8499,32 +8499,32 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>709894</t>
+          <t>301258</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SANTA MARIA LA REINA</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>-11.914505</t>
+          <t>678</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>-77.035188</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>-11.93058</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-77.05648</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -8561,37 +8561,37 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>711482</t>
+          <t>301215</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>DELTA</t>
+          <t>328</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>-11.9053</t>
+          <t>284</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>-77.04044</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-11.90765</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-77.03788</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8623,42 +8623,42 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>301705</t>
+          <t>301201</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026 SIMON BOLIVAR</t>
+          <t>316 SAN FELIPE</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>-11.95063</t>
+          <t>264</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>-77.06313</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>-11.90046</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-77.04003</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8685,32 +8685,32 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>333278</t>
+          <t>301197</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>3024 JOSE ANTONIO ENCINAS</t>
+          <t>054</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>-11.94278</t>
+          <t>362</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>-77.06833</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>-11.959535</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-77.04419</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8747,32 +8747,32 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>301692</t>
+          <t>301183</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>LIBERTAD</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>-11.9224</t>
+          <t>379</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>-77.03899</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>-11.9381</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-77.04256</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8809,32 +8809,32 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>301814</t>
+          <t>301178</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2031 JOSE VALVERDE CARO</t>
+          <t>02 JOSE GALVITO</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>-11.94512</t>
+          <t>208</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>-77.03126</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>-11.911038</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-77.012883</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8871,32 +8871,32 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>303752</t>
+          <t>301164</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 10</t>
+          <t>368 ANGELITOS DE JESUS</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>-11.91727</t>
+          <t>388</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>-77.0406</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>-11.91963</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-77.05964</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8933,32 +8933,32 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>801524</t>
+          <t>301159</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>TECHNOLOGY SCHOOLS DEL RETABLO I</t>
+          <t>371</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>-11.93572</t>
+          <t>312</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>-77.05902</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>-11.94334</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>-77.05569</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8995,32 +8995,32 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>303554</t>
+          <t>301140</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 11</t>
+          <t>LUIS ENRIQUE XIII</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>-11.91561</t>
+          <t>275</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>-77.02516</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>-11.90842</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-77.04148</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -9057,32 +9057,32 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>301871</t>
+          <t>301135</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>MARISCAL ANDRES AVELINO CACERES DORREGARAY</t>
+          <t>LUIS ENRIQUE II</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>-11.91639</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>-77.03376</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>-11.91925</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-77.03833</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9119,32 +9119,32 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>301913</t>
+          <t>301121</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>SAN FELIPE</t>
+          <t>888 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>-11.89896</t>
+          <t>331</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>-77.04063</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>-11.91563</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-77.03456</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9181,32 +9181,32 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>303568</t>
+          <t>301116</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 13</t>
+          <t>CARMEN ALTO</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>-11.9128</t>
+          <t>304</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>-77.0094</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>1745</t>
+          <t>-11.94631</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-77.03114</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -9243,32 +9243,32 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>301748</t>
+          <t>301102</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>3047 REPUBLICA DE CANADA</t>
+          <t>868</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>-11.95916</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>-77.04107</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>-11.9098</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>-77.04598</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -9305,32 +9305,32 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>303733</t>
+          <t>301041</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>PRESENTACION DE MARIA 41</t>
+          <t>373</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>-11.95058</t>
+          <t>216</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>-77.05162</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>-11.95157</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>-77.0574</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -9367,37 +9367,37 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>549264</t>
+          <t>301036</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>SONIA AMADOR JAIME II</t>
+          <t>370 VIRGEN DE LA PUERTA</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>-11.95313</t>
+          <t>241</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>-77.05053</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-11.95692</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-77.03582</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9429,32 +9429,32 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>301687</t>
+          <t>301022</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>PERU-HOLANDA</t>
+          <t>369</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>-11.91663</t>
+          <t>240</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>-77.03561</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>1745</t>
+          <t>-11.93322</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>-77.05404</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -9491,32 +9491,32 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>301625</t>
+          <t>301017</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2048 JOSE CARLOS MARIATEGUI</t>
+          <t>356 ANGELITOS DEL ALAMO</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>-11.939926</t>
+          <t>240</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>-77.063361</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>-11.93107</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>-77.06794</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -9553,42 +9553,42 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>301772</t>
+          <t>301003</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2085 SAN AGUSTIN</t>
+          <t>354 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>-11.9323</t>
+          <t>167</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>-77.05056</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>-11.92742</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>-77.056</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9615,32 +9615,32 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>303894</t>
+          <t>300980</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SARITA COLONIA</t>
+          <t>341 EL RETABLO</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>-11.92516</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>-77.04167</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>-11.93803</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-77.05577</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -9677,37 +9677,37 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>304290</t>
+          <t>300975</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>SONIA AMADOR JAIME</t>
+          <t>337 SANGARARA</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>-11.95381</t>
+          <t>265</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>-77.05101</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>-11.92474</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-77.04515</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -9739,32 +9739,32 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>301611</t>
+          <t>300961</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2022 SINCHI ROCA</t>
+          <t>334</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>-11.93045</t>
+          <t>348</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>-77.04964</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>-11.94098</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>-77.06309</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9801,32 +9801,32 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>301630</t>
+          <t>300956</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>3055 TUPAC AMARU</t>
+          <t>326 MARIA MONTESSORI</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>-11.93503</t>
+          <t>296</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>-77.04317</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>-11.95697</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>-77.05621</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9863,32 +9863,32 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>301178</t>
+          <t>300937</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>02 JOSE GALVITO</t>
+          <t>317</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>-11.911038</t>
+          <t>237</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>-77.012883</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>-11.92047</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-77.04411</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9925,32 +9925,32 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>304148</t>
+          <t>300918</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>JAIME WHITE</t>
+          <t>03</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>-11.936118</t>
+          <t>209</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>-77.044542</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>-11.9662</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-77.05441</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -9987,37 +9987,37 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>398095</t>
+          <t>300895</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>MI PEQUEÑO MUNDO DE SANTA LUZMILA</t>
+          <t>LUIS ENRIQUE XIV</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>-11.94454</t>
+          <t>290</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>-77.06369</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>-11.9141</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-77.0112</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -10049,37 +10049,37 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>526917</t>
+          <t>300881</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>JESUS, NUESTRO AMIGO DE LA LIBERTAD</t>
+          <t>SANGARARA</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>-11.95754</t>
+          <t>336</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>-77.04913</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>-11.915543</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-77.055633</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -10111,42 +10111,42 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>301932</t>
+          <t>300876</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>CARLOS WIESSE</t>
+          <t>LA PASCANA</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>-11.9519</t>
+          <t>390</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>-77.0505</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>-11.93643</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>-77.04637</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -10173,32 +10173,32 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>301649</t>
+          <t>230713</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>ESTADOS UNIDOS</t>
+          <t>MARIO VARGAS LLOSA</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>-11.965191</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>-77.05676</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>-11.92458</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>-77.05362</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10235,32 +10235,32 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>304266</t>
+          <t>014945</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>LICEO SANTO DOMINGO</t>
+          <t>ANGELITOS DE SANTA MARIA</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>-11.91322</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>-77.05263</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>-11.91243</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>-77.02597</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-COMAS.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-COMAS.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
